--- a/p_gps_pts.xlsx
+++ b/p_gps_pts.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stateofwa-my.sharepoint.com/personal/peter_dowty_dnr_wa_gov/Documents/projects/seagrass_restoration_data_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{482DCFCD-CB29-4C6F-A4E2-D15E2062173E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{482DCFCD-CB29-4C6F-A4E2-D15E2062173E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C04B233-E9A2-4D28-9E31-7FF6BE17617E}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="90" windowWidth="28320" windowHeight="15330" xr2:uid="{472C6C18-3318-42E5-B3DE-BCE9F97FEFF7}"/>
+    <workbookView xWindow="90" yWindow="45" windowWidth="28320" windowHeight="15330" xr2:uid="{472C6C18-3318-42E5-B3DE-BCE9F97FEFF7}"/>
   </bookViews>
   <sheets>
     <sheet name="p_gps_pts" sheetId="1" r:id="rId1"/>
@@ -2633,7 +2633,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2647,16 +2647,17 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3033,7 +3034,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DC67150-E300-40D7-8142-428F73FC9A10}">
   <dimension ref="A1:AE289"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.85546875" bestFit="1" customWidth="1"/>
@@ -3067,7 +3068,7 @@
     <col min="31" max="31" width="36" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -3159,7 +3160,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3254,7 +3255,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3349,7 +3350,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3444,7 +3445,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3539,7 +3540,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3634,7 +3635,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3729,7 +3730,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3824,7 +3825,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3919,7 +3920,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4014,7 +4015,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4109,7 +4110,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4204,7 +4205,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4299,7 +4300,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4394,7 +4395,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4489,7 +4490,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4584,7 +4585,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4679,7 +4680,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4774,7 +4775,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4869,7 +4870,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4964,7 +4965,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -5059,7 +5060,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -5154,7 +5155,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -5249,7 +5250,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="24" spans="1:31" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -5344,7 +5345,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="25" spans="1:31" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -5439,7 +5440,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="26" spans="1:31" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -5534,7 +5535,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="27" spans="1:31" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -5629,7 +5630,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="28" spans="1:31" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>27</v>
       </c>
@@ -5724,7 +5725,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -5819,7 +5820,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -5914,7 +5915,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -6009,7 +6010,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -6104,7 +6105,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -6199,7 +6200,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -6294,7 +6295,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -6389,7 +6390,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -6484,197 +6485,197 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A37">
+    <row r="37" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="4">
         <v>36</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="4">
         <v>2016</v>
       </c>
-      <c r="G37" t="s">
+      <c r="G37" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="H37" s="3" t="s">
+      <c r="H37" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="I37" t="s">
+      <c r="I37" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="J37" t="s">
+      <c r="J37" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K37" t="s">
-        <v>38</v>
-      </c>
-      <c r="L37" t="s">
-        <v>38</v>
-      </c>
-      <c r="M37" s="1">
+      <c r="K37" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="L37" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="M37" s="6">
         <v>42481</v>
       </c>
-      <c r="N37">
+      <c r="N37" s="4">
         <v>47.258040352777797</v>
       </c>
-      <c r="O37">
+      <c r="O37" s="4">
         <v>-122.739271322222</v>
       </c>
-      <c r="P37" t="s">
+      <c r="P37" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="Q37" t="s">
-        <v>40</v>
-      </c>
-      <c r="R37">
+      <c r="Q37" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="R37" s="4">
         <v>-2</v>
       </c>
-      <c r="S37" t="s">
+      <c r="S37" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="T37">
+      <c r="T37" s="4">
         <v>25</v>
       </c>
-      <c r="U37">
+      <c r="U37" s="4">
         <v>5</v>
       </c>
-      <c r="V37">
+      <c r="V37" s="4">
         <v>125</v>
       </c>
-      <c r="W37">
+      <c r="W37" s="4">
         <v>75</v>
       </c>
-      <c r="X37">
+      <c r="X37" s="4">
         <v>9.75</v>
       </c>
-      <c r="Y37">
+      <c r="Y37" s="4">
         <v>156</v>
       </c>
-      <c r="Z37">
+      <c r="Z37" s="4">
         <v>780</v>
       </c>
-      <c r="AA37">
+      <c r="AA37" s="4">
         <v>6.24</v>
       </c>
-      <c r="AB37">
+      <c r="AB37" s="4">
         <v>10.4</v>
       </c>
-      <c r="AC37" t="s">
+      <c r="AC37" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="AD37" t="s">
+      <c r="AD37" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="AE37" t="s">
+      <c r="AE37" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A38">
+    <row r="38" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="4">
         <v>37</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F38">
+      <c r="F38" s="4">
         <v>2016</v>
       </c>
-      <c r="G38" t="s">
+      <c r="G38" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="H38" s="3" t="s">
+      <c r="H38" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="I38" t="s">
+      <c r="I38" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="J38" t="s">
+      <c r="J38" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K38" t="s">
-        <v>38</v>
-      </c>
-      <c r="L38" t="s">
+      <c r="K38" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="L38" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M38" s="1">
+      <c r="M38" s="6">
         <v>42481</v>
       </c>
-      <c r="N38">
+      <c r="N38" s="4">
         <v>47.258279688888898</v>
       </c>
-      <c r="O38">
+      <c r="O38" s="4">
         <v>-122.7380948</v>
       </c>
-      <c r="P38" t="s">
+      <c r="P38" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="Q38" t="s">
-        <v>40</v>
-      </c>
-      <c r="R38">
+      <c r="Q38" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="R38" s="4">
         <v>-2</v>
       </c>
-      <c r="S38" t="s">
+      <c r="S38" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="T38" t="s">
-        <v>43</v>
-      </c>
-      <c r="U38" t="s">
-        <v>43</v>
-      </c>
-      <c r="V38" t="s">
-        <v>43</v>
-      </c>
-      <c r="W38" t="s">
-        <v>43</v>
-      </c>
-      <c r="X38" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y38" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z38" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA38" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB38" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC38" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD38" t="s">
-        <v>43</v>
-      </c>
-      <c r="AE38" t="s">
+      <c r="T38" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="U38" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="V38" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="W38" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X38" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y38" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z38" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA38" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB38" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC38" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD38" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE38" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -6769,7 +6770,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -6864,7 +6865,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -6959,7 +6960,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -7054,7 +7055,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="43" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -7149,7 +7150,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="44" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -7244,7 +7245,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="45" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -7339,7 +7340,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="46" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -7434,7 +7435,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="47" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -7529,7 +7530,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="48" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -7624,7 +7625,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="49" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -7719,7 +7720,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="50" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -7814,7 +7815,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="51" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -7909,7 +7910,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="52" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -8004,387 +8005,387 @@
         <v>183</v>
       </c>
     </row>
-    <row r="53" spans="1:31" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="7">
+    <row r="53" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53">
         <v>52</v>
       </c>
-      <c r="B53" s="7" t="s">
+      <c r="B53" t="s">
         <v>112</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="C53" t="s">
         <v>184</v>
       </c>
-      <c r="D53" s="7" t="s">
+      <c r="D53" t="s">
         <v>185</v>
       </c>
-      <c r="E53" s="7" t="s">
+      <c r="E53" t="s">
         <v>33</v>
       </c>
-      <c r="F53" s="7">
+      <c r="F53">
         <v>2021</v>
       </c>
-      <c r="G53" s="7" t="s">
+      <c r="G53" t="s">
         <v>110</v>
       </c>
-      <c r="H53" s="8" t="s">
+      <c r="H53" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="I53" s="7" t="s">
+      <c r="I53" t="s">
         <v>181</v>
       </c>
-      <c r="J53" s="7" t="s">
+      <c r="J53" t="s">
         <v>37</v>
       </c>
-      <c r="K53" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="L53" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="M53" s="9">
+      <c r="K53" t="s">
+        <v>38</v>
+      </c>
+      <c r="L53" t="s">
+        <v>38</v>
+      </c>
+      <c r="M53" s="1">
         <v>44314</v>
       </c>
-      <c r="N53" s="7">
+      <c r="N53">
         <v>47.329329999999999</v>
       </c>
-      <c r="O53" s="7">
+      <c r="O53">
         <v>-122.38615</v>
       </c>
-      <c r="P53" s="7" t="s">
+      <c r="P53" t="s">
         <v>39</v>
       </c>
-      <c r="Q53" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="R53" s="7">
+      <c r="Q53" t="s">
+        <v>40</v>
+      </c>
+      <c r="R53">
         <v>-1.6</v>
       </c>
-      <c r="S53" s="7" t="s">
+      <c r="S53" t="s">
         <v>54</v>
       </c>
-      <c r="T53" s="7">
+      <c r="T53">
         <v>3.5</v>
       </c>
-      <c r="U53" s="7">
+      <c r="U53">
         <v>3.5</v>
       </c>
-      <c r="V53" s="7">
+      <c r="V53">
         <v>12.25</v>
       </c>
-      <c r="W53" s="7">
+      <c r="W53">
         <v>1</v>
       </c>
-      <c r="X53" s="7">
+      <c r="X53">
         <v>0.3</v>
       </c>
-      <c r="Y53" s="7">
+      <c r="Y53">
         <v>12</v>
       </c>
-      <c r="Z53" s="7">
+      <c r="Z53">
         <v>300</v>
       </c>
-      <c r="AA53" s="7">
+      <c r="AA53">
         <v>24.4897959183673</v>
       </c>
-      <c r="AB53" s="7">
+      <c r="AB53">
         <v>300</v>
       </c>
-      <c r="AC53" s="7" t="s">
+      <c r="AC53" t="s">
         <v>112</v>
       </c>
-      <c r="AD53" s="7" t="s">
+      <c r="AD53" t="s">
         <v>186</v>
       </c>
-      <c r="AE53" s="7" t="s">
+      <c r="AE53" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="54" spans="1:31" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="7">
+    <row r="54" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54">
         <v>53</v>
       </c>
-      <c r="B54" s="7" t="s">
+      <c r="B54" t="s">
         <v>112</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="C54" t="s">
         <v>184</v>
       </c>
-      <c r="D54" s="7" t="s">
+      <c r="D54" t="s">
         <v>185</v>
       </c>
-      <c r="E54" s="7" t="s">
+      <c r="E54" t="s">
         <v>33</v>
       </c>
-      <c r="F54" s="7">
+      <c r="F54">
         <v>2021</v>
       </c>
-      <c r="G54" s="7" t="s">
+      <c r="G54" t="s">
         <v>110</v>
       </c>
-      <c r="H54" s="8" t="s">
+      <c r="H54" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="I54" s="7" t="s">
+      <c r="I54" t="s">
         <v>181</v>
       </c>
-      <c r="J54" s="7" t="s">
+      <c r="J54" t="s">
         <v>37</v>
       </c>
-      <c r="K54" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="L54" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="M54" s="9">
+      <c r="K54" t="s">
+        <v>38</v>
+      </c>
+      <c r="L54" t="s">
+        <v>38</v>
+      </c>
+      <c r="M54" s="1">
         <v>44329</v>
       </c>
-      <c r="N54" s="7">
+      <c r="N54">
         <v>47.329329999999999</v>
       </c>
-      <c r="O54" s="7">
+      <c r="O54">
         <v>-122.38615</v>
       </c>
-      <c r="P54" s="7" t="s">
+      <c r="P54" t="s">
         <v>39</v>
       </c>
-      <c r="Q54" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="R54" s="7">
+      <c r="Q54" t="s">
+        <v>40</v>
+      </c>
+      <c r="R54">
         <v>-1.6</v>
       </c>
-      <c r="S54" s="7" t="s">
+      <c r="S54" t="s">
         <v>54</v>
       </c>
-      <c r="T54" s="7">
+      <c r="T54">
         <v>3.5</v>
       </c>
-      <c r="U54" s="7">
+      <c r="U54">
         <v>0.5</v>
       </c>
-      <c r="V54" s="7">
+      <c r="V54">
         <v>1.75</v>
       </c>
-      <c r="W54" s="7">
+      <c r="W54">
         <v>0.75</v>
       </c>
-      <c r="X54" s="7">
+      <c r="X54">
         <v>0.22500000000000001</v>
       </c>
-      <c r="Y54" s="7">
+      <c r="Y54">
         <v>9</v>
       </c>
-      <c r="Z54" s="7">
+      <c r="Z54">
         <v>180</v>
       </c>
-      <c r="AA54" s="7">
+      <c r="AA54">
         <v>102.857142857143</v>
       </c>
-      <c r="AB54" s="7">
+      <c r="AB54">
         <v>240</v>
       </c>
-      <c r="AC54" s="7" t="s">
+      <c r="AC54" t="s">
         <v>98</v>
       </c>
-      <c r="AD54" s="7" t="s">
+      <c r="AD54" t="s">
         <v>187</v>
       </c>
-      <c r="AE54" s="7" t="s">
+      <c r="AE54" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="55" spans="1:31" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="7">
+    <row r="55" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55">
         <v>54</v>
       </c>
-      <c r="B55" s="7" t="s">
+      <c r="B55" t="s">
         <v>112</v>
       </c>
-      <c r="C55" s="7" t="s">
+      <c r="C55" t="s">
         <v>184</v>
       </c>
-      <c r="D55" s="7" t="s">
+      <c r="D55" t="s">
         <v>185</v>
       </c>
-      <c r="E55" s="7" t="s">
+      <c r="E55" t="s">
         <v>33</v>
       </c>
-      <c r="F55" s="7">
+      <c r="F55">
         <v>2021</v>
       </c>
-      <c r="G55" s="7" t="s">
+      <c r="G55" t="s">
         <v>110</v>
       </c>
-      <c r="H55" s="8" t="s">
+      <c r="H55" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="I55" s="7" t="s">
+      <c r="I55" t="s">
         <v>181</v>
       </c>
-      <c r="J55" s="7" t="s">
+      <c r="J55" t="s">
         <v>37</v>
       </c>
-      <c r="K55" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="L55" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="M55" s="9">
+      <c r="K55" t="s">
+        <v>38</v>
+      </c>
+      <c r="L55" t="s">
+        <v>38</v>
+      </c>
+      <c r="M55" s="1">
         <v>44342</v>
       </c>
-      <c r="N55" s="7">
+      <c r="N55">
         <v>47.329329999999999</v>
       </c>
-      <c r="O55" s="7">
+      <c r="O55">
         <v>-122.38615</v>
       </c>
-      <c r="P55" s="7" t="s">
+      <c r="P55" t="s">
         <v>39</v>
       </c>
-      <c r="Q55" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="R55" s="7">
+      <c r="Q55" t="s">
+        <v>40</v>
+      </c>
+      <c r="R55">
         <v>-1.6</v>
       </c>
-      <c r="S55" s="7" t="s">
+      <c r="S55" t="s">
         <v>54</v>
       </c>
-      <c r="T55" s="7">
+      <c r="T55">
         <v>3.5</v>
       </c>
-      <c r="U55" s="7">
+      <c r="U55">
         <v>0.5</v>
       </c>
-      <c r="V55" s="7">
+      <c r="V55">
         <v>1.75</v>
       </c>
-      <c r="W55" s="7">
+      <c r="W55">
         <v>0.75</v>
       </c>
-      <c r="X55" s="7">
+      <c r="X55">
         <v>0.22500000000000001</v>
       </c>
-      <c r="Y55" s="7">
+      <c r="Y55">
         <v>9</v>
       </c>
-      <c r="Z55" s="7">
+      <c r="Z55">
         <v>180</v>
       </c>
-      <c r="AA55" s="7">
+      <c r="AA55">
         <v>102.857142857143</v>
       </c>
-      <c r="AB55" s="7">
+      <c r="AB55">
         <v>240</v>
       </c>
-      <c r="AC55" s="7" t="s">
+      <c r="AC55" t="s">
         <v>98</v>
       </c>
-      <c r="AD55" s="7" t="s">
+      <c r="AD55" t="s">
         <v>188</v>
       </c>
-      <c r="AE55" s="7" t="s">
+      <c r="AE55" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="56" spans="1:31" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="7">
+    <row r="56" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56">
         <v>55</v>
       </c>
-      <c r="B56" s="7" t="s">
+      <c r="B56" t="s">
         <v>112</v>
       </c>
-      <c r="C56" s="7" t="s">
+      <c r="C56" t="s">
         <v>184</v>
       </c>
-      <c r="D56" s="7" t="s">
+      <c r="D56" t="s">
         <v>185</v>
       </c>
-      <c r="E56" s="7" t="s">
+      <c r="E56" t="s">
         <v>33</v>
       </c>
-      <c r="F56" s="7">
+      <c r="F56">
         <v>2021</v>
       </c>
-      <c r="G56" s="7" t="s">
+      <c r="G56" t="s">
         <v>110</v>
       </c>
-      <c r="H56" s="8" t="s">
+      <c r="H56" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="I56" s="7" t="s">
+      <c r="I56" t="s">
         <v>181</v>
       </c>
-      <c r="J56" s="7" t="s">
+      <c r="J56" t="s">
         <v>37</v>
       </c>
-      <c r="K56" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="L56" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="M56" s="9">
+      <c r="K56" t="s">
+        <v>38</v>
+      </c>
+      <c r="L56" t="s">
+        <v>38</v>
+      </c>
+      <c r="M56" s="1">
         <v>44373</v>
       </c>
-      <c r="N56" s="7">
+      <c r="N56">
         <v>47.329329999999999</v>
       </c>
-      <c r="O56" s="7">
+      <c r="O56">
         <v>-122.38615</v>
       </c>
-      <c r="P56" s="7" t="s">
+      <c r="P56" t="s">
         <v>39</v>
       </c>
-      <c r="Q56" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="R56" s="7">
+      <c r="Q56" t="s">
+        <v>40</v>
+      </c>
+      <c r="R56">
         <v>-1.6</v>
       </c>
-      <c r="S56" s="7" t="s">
+      <c r="S56" t="s">
         <v>54</v>
       </c>
-      <c r="T56" s="7">
+      <c r="T56">
         <v>3.5</v>
       </c>
-      <c r="U56" s="7">
+      <c r="U56">
         <v>2</v>
       </c>
-      <c r="V56" s="7">
+      <c r="V56">
         <v>7</v>
       </c>
-      <c r="W56" s="7">
+      <c r="W56">
         <v>1.5</v>
       </c>
-      <c r="X56" s="7">
+      <c r="X56">
         <v>0.45</v>
       </c>
-      <c r="Y56" s="7">
+      <c r="Y56">
         <v>18</v>
       </c>
-      <c r="Z56" s="7">
+      <c r="Z56">
         <v>270</v>
       </c>
-      <c r="AA56" s="7">
+      <c r="AA56">
         <v>38.571428571428598</v>
       </c>
-      <c r="AB56" s="7">
+      <c r="AB56">
         <v>180</v>
       </c>
-      <c r="AC56" s="7" t="s">
+      <c r="AC56" t="s">
         <v>98</v>
       </c>
-      <c r="AD56" s="7" t="s">
+      <c r="AD56" t="s">
         <v>189</v>
       </c>
-      <c r="AE56" s="7" t="s">
+      <c r="AE56" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="57" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -8479,7 +8480,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="58" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -8574,7 +8575,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="59" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -8669,7 +8670,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="60" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -8764,7 +8765,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="61" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -8859,7 +8860,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="62" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -8954,7 +8955,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="63" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -9049,7 +9050,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="64" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -9144,7 +9145,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="65" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -9239,7 +9240,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="66" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -9334,7 +9335,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="67" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -9429,7 +9430,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -9524,7 +9525,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="69" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
@@ -9619,7 +9620,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="70" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
@@ -9714,7 +9715,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="71" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -9809,7 +9810,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="72" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -9904,7 +9905,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="73" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -9999,7 +10000,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -10094,7 +10095,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="75" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
@@ -10189,7 +10190,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="76" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -10284,7 +10285,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="77" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
@@ -10379,7 +10380,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="78" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
@@ -10474,7 +10475,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="79" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
@@ -10569,7 +10570,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="80" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
@@ -10664,7 +10665,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="81" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
@@ -10759,7 +10760,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="82" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
@@ -10854,7 +10855,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="83" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
@@ -10949,7 +10950,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="84" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
@@ -11044,7 +11045,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="85" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
@@ -11139,7 +11140,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="86" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
@@ -11234,7 +11235,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="87" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
@@ -11329,7 +11330,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="88" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
@@ -11424,7 +11425,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="89" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
@@ -11519,7 +11520,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="90" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
@@ -11614,7 +11615,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="91" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
@@ -11709,7 +11710,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="92" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
@@ -11804,7 +11805,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="93" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
@@ -11899,7 +11900,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="94" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
@@ -11994,7 +11995,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="95" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
@@ -12089,7 +12090,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="96" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
@@ -12184,767 +12185,767 @@
         <v>44</v>
       </c>
     </row>
-    <row r="97" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A97">
+    <row r="97" spans="1:31" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="7">
         <v>96</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C97" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="D97" t="s">
+      <c r="D97" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="E97" t="s">
+      <c r="E97" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="F97">
+      <c r="F97" s="7">
         <v>2015</v>
       </c>
-      <c r="G97" t="s">
-        <v>43</v>
-      </c>
-      <c r="H97" s="3" t="s">
+      <c r="G97" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H97" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="I97" t="s">
+      <c r="I97" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="J97" t="s">
+      <c r="J97" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="K97" t="s">
+      <c r="K97" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="L97" t="s">
+      <c r="L97" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="M97" s="1">
+      <c r="M97" s="9">
         <v>42141</v>
       </c>
-      <c r="N97">
+      <c r="N97" s="7">
         <v>47.222349999999999</v>
       </c>
-      <c r="O97">
+      <c r="O97" s="7">
         <v>-122.8105</v>
       </c>
-      <c r="P97" t="s">
+      <c r="P97" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="Q97" t="s">
-        <v>40</v>
-      </c>
-      <c r="R97" t="s">
-        <v>43</v>
-      </c>
-      <c r="S97" t="s">
+      <c r="Q97" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="R97" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="S97" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="T97">
+      <c r="T97" s="7">
         <v>50</v>
       </c>
-      <c r="U97">
-        <v>40</v>
-      </c>
-      <c r="V97">
+      <c r="U97" s="7">
+        <v>40</v>
+      </c>
+      <c r="V97" s="7">
         <v>2000</v>
       </c>
-      <c r="W97">
+      <c r="W97" s="7">
         <v>126.25</v>
       </c>
-      <c r="X97">
+      <c r="X97" s="7">
         <v>12.75</v>
       </c>
-      <c r="Y97">
+      <c r="Y97" s="7">
         <v>2550</v>
       </c>
-      <c r="Z97">
+      <c r="Z97" s="7">
         <v>10200</v>
       </c>
-      <c r="AA97">
+      <c r="AA97" s="7">
         <v>5.0999999999999996</v>
       </c>
-      <c r="AB97">
+      <c r="AB97" s="7">
         <v>80.792079207920807</v>
       </c>
-      <c r="AC97" t="s">
+      <c r="AC97" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="AD97" t="s">
+      <c r="AD97" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="AE97" t="s">
+      <c r="AE97" s="7" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="98" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A98">
+    <row r="98" spans="1:31" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="7">
         <v>97</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C98" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="D98" t="s">
+      <c r="D98" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="E98" t="s">
+      <c r="E98" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="F98">
+      <c r="F98" s="7">
         <v>2015</v>
       </c>
-      <c r="G98" t="s">
-        <v>43</v>
-      </c>
-      <c r="H98" s="3" t="s">
+      <c r="G98" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H98" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="I98" t="s">
+      <c r="I98" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="J98" t="s">
+      <c r="J98" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="K98" t="s">
+      <c r="K98" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="L98" t="s">
+      <c r="L98" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="M98" s="1">
+      <c r="M98" s="9">
         <v>42141</v>
       </c>
-      <c r="N98">
+      <c r="N98" s="7">
         <v>47.222516666666699</v>
       </c>
-      <c r="O98">
+      <c r="O98" s="7">
         <v>-122.810033333333</v>
       </c>
-      <c r="P98" t="s">
+      <c r="P98" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="Q98" t="s">
-        <v>40</v>
-      </c>
-      <c r="R98" t="s">
-        <v>43</v>
-      </c>
-      <c r="S98" t="s">
+      <c r="Q98" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="R98" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="S98" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="T98" t="s">
-        <v>43</v>
-      </c>
-      <c r="U98" t="s">
-        <v>43</v>
-      </c>
-      <c r="V98" t="s">
-        <v>43</v>
-      </c>
-      <c r="W98" t="s">
-        <v>43</v>
-      </c>
-      <c r="X98" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y98" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z98" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA98" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB98" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC98" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD98" t="s">
+      <c r="T98" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="U98" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="V98" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="W98" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X98" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y98" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z98" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA98" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB98" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC98" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD98" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="AE98" t="s">
+      <c r="AE98" s="7" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="99" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A99">
+    <row r="99" spans="1:31" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="7">
         <v>98</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="C99" t="s">
+      <c r="C99" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="D99" t="s">
+      <c r="D99" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="E99" t="s">
+      <c r="E99" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="F99">
+      <c r="F99" s="7">
         <v>2015</v>
       </c>
-      <c r="G99" t="s">
-        <v>43</v>
-      </c>
-      <c r="H99" s="3" t="s">
+      <c r="G99" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H99" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="I99" t="s">
+      <c r="I99" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="J99" t="s">
+      <c r="J99" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="K99" t="s">
+      <c r="K99" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="L99" t="s">
+      <c r="L99" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="M99" s="1">
+      <c r="M99" s="9">
         <v>42141</v>
       </c>
-      <c r="N99">
+      <c r="N99" s="7">
         <v>47.222149999999999</v>
       </c>
-      <c r="O99">
+      <c r="O99" s="7">
         <v>-122.809666666667</v>
       </c>
-      <c r="P99" t="s">
+      <c r="P99" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="Q99" t="s">
-        <v>40</v>
-      </c>
-      <c r="R99">
+      <c r="Q99" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="R99" s="7">
         <v>-0.91439999999999999</v>
       </c>
-      <c r="S99" t="s">
+      <c r="S99" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="T99" t="s">
-        <v>43</v>
-      </c>
-      <c r="U99" t="s">
-        <v>43</v>
-      </c>
-      <c r="V99" t="s">
-        <v>43</v>
-      </c>
-      <c r="W99" t="s">
-        <v>43</v>
-      </c>
-      <c r="X99" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y99" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z99" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA99" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB99" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC99" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD99" t="s">
+      <c r="T99" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="U99" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="V99" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="W99" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X99" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y99" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z99" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA99" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB99" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC99" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD99" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="AE99" t="s">
+      <c r="AE99" s="7" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="100" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A100">
+    <row r="100" spans="1:31" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="7">
         <v>99</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="C100" t="s">
+      <c r="C100" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="D100" t="s">
+      <c r="D100" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="E100" t="s">
+      <c r="E100" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="F100">
+      <c r="F100" s="7">
         <v>2015</v>
       </c>
-      <c r="G100" t="s">
-        <v>43</v>
-      </c>
-      <c r="H100" s="3" t="s">
+      <c r="G100" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H100" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="I100" t="s">
+      <c r="I100" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="J100" t="s">
+      <c r="J100" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="K100" t="s">
+      <c r="K100" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="L100" t="s">
+      <c r="L100" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="M100" s="1">
+      <c r="M100" s="9">
         <v>42141</v>
       </c>
-      <c r="N100">
+      <c r="N100" s="7">
         <v>47.222000000000001</v>
       </c>
-      <c r="O100">
+      <c r="O100" s="7">
         <v>-122.810083333333</v>
       </c>
-      <c r="P100" t="s">
+      <c r="P100" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="Q100" t="s">
-        <v>40</v>
-      </c>
-      <c r="R100">
+      <c r="Q100" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="R100" s="7">
         <v>-1.524</v>
       </c>
-      <c r="S100" t="s">
+      <c r="S100" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="T100" t="s">
-        <v>43</v>
-      </c>
-      <c r="U100" t="s">
-        <v>43</v>
-      </c>
-      <c r="V100" t="s">
-        <v>43</v>
-      </c>
-      <c r="W100" t="s">
-        <v>43</v>
-      </c>
-      <c r="X100" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y100" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z100" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA100" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB100" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC100" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD100" t="s">
+      <c r="T100" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="U100" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="V100" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="W100" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X100" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y100" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z100" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA100" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB100" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC100" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD100" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="AE100" t="s">
+      <c r="AE100" s="7" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="101" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A101">
+    <row r="101" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="4">
         <v>100</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C101" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="D101" t="s">
+      <c r="D101" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="E101" t="s">
+      <c r="E101" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F101">
+      <c r="F101" s="4">
         <v>2015</v>
       </c>
-      <c r="G101" t="s">
-        <v>43</v>
-      </c>
-      <c r="H101" s="3" t="s">
+      <c r="G101" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H101" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="I101" t="s">
+      <c r="I101" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="J101" t="s">
+      <c r="J101" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K101" t="s">
+      <c r="K101" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="L101" t="s">
+      <c r="L101" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="M101" s="1">
+      <c r="M101" s="6">
         <v>42162</v>
       </c>
-      <c r="N101">
+      <c r="N101" s="4">
         <v>47.223383333333302</v>
       </c>
-      <c r="O101">
+      <c r="O101" s="4">
         <v>-122.810666666667</v>
       </c>
-      <c r="P101" t="s">
+      <c r="P101" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="Q101" t="s">
-        <v>40</v>
-      </c>
-      <c r="R101">
+      <c r="Q101" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="R101" s="4">
         <v>-1.28016</v>
       </c>
-      <c r="S101" t="s">
+      <c r="S101" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="T101">
+      <c r="T101" s="4">
         <v>60</v>
       </c>
-      <c r="U101">
-        <v>40</v>
-      </c>
-      <c r="V101">
+      <c r="U101" s="4">
+        <v>40</v>
+      </c>
+      <c r="V101" s="4">
         <v>2400</v>
       </c>
-      <c r="W101">
+      <c r="W101" s="4">
         <v>151.25</v>
       </c>
-      <c r="X101">
+      <c r="X101" s="4">
         <v>15</v>
       </c>
-      <c r="Y101">
+      <c r="Y101" s="4">
         <v>3000</v>
       </c>
-      <c r="Z101">
+      <c r="Z101" s="4">
         <v>12000</v>
       </c>
-      <c r="AA101">
+      <c r="AA101" s="4">
         <v>5</v>
       </c>
-      <c r="AB101">
+      <c r="AB101" s="4">
         <v>79.338842975206603</v>
       </c>
-      <c r="AC101" t="s">
+      <c r="AC101" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="AD101" t="s">
+      <c r="AD101" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="AE101" t="s">
+      <c r="AE101" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="102" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A102">
+    <row r="102" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="4">
         <v>101</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C102" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="D102" t="s">
+      <c r="D102" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="E102" t="s">
+      <c r="E102" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F102">
+      <c r="F102" s="4">
         <v>2015</v>
       </c>
-      <c r="G102" t="s">
-        <v>43</v>
-      </c>
-      <c r="H102" s="3" t="s">
+      <c r="G102" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H102" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="I102" t="s">
+      <c r="I102" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="J102" t="s">
+      <c r="J102" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K102" t="s">
+      <c r="K102" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="L102" t="s">
+      <c r="L102" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M102" s="1">
+      <c r="M102" s="6">
         <v>42162</v>
       </c>
-      <c r="N102">
+      <c r="N102" s="4">
         <v>47.223383333333302</v>
       </c>
-      <c r="O102">
+      <c r="O102" s="4">
         <v>-122.81014999999999</v>
       </c>
-      <c r="P102" t="s">
+      <c r="P102" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="Q102" t="s">
-        <v>40</v>
-      </c>
-      <c r="R102">
+      <c r="Q102" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="R102" s="4">
         <v>-0.51815999999999995</v>
       </c>
-      <c r="S102" t="s">
+      <c r="S102" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="T102" t="s">
-        <v>43</v>
-      </c>
-      <c r="U102" t="s">
-        <v>43</v>
-      </c>
-      <c r="V102" t="s">
-        <v>43</v>
-      </c>
-      <c r="W102" t="s">
-        <v>43</v>
-      </c>
-      <c r="X102" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y102" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z102" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA102" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB102" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC102" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD102" t="s">
+      <c r="T102" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="U102" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="V102" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="W102" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X102" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y102" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z102" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA102" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB102" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC102" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD102" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="AE102" t="s">
+      <c r="AE102" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="103" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A103">
+    <row r="103" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="4">
         <v>102</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C103" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="D103" t="s">
+      <c r="D103" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="E103" t="s">
+      <c r="E103" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F103">
+      <c r="F103" s="4">
         <v>2015</v>
       </c>
-      <c r="G103" t="s">
-        <v>43</v>
-      </c>
-      <c r="H103" s="3" t="s">
+      <c r="G103" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H103" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="I103" t="s">
+      <c r="I103" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="J103" t="s">
+      <c r="J103" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K103" t="s">
+      <c r="K103" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="L103" t="s">
+      <c r="L103" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M103" s="1">
+      <c r="M103" s="6">
         <v>42162</v>
       </c>
-      <c r="N103">
+      <c r="N103" s="4">
         <v>47.222833333333298</v>
       </c>
-      <c r="O103">
+      <c r="O103" s="4">
         <v>-122.81014999999999</v>
       </c>
-      <c r="P103" t="s">
+      <c r="P103" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="Q103" t="s">
-        <v>40</v>
-      </c>
-      <c r="R103">
+      <c r="Q103" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="R103" s="4">
         <v>-0.97536</v>
       </c>
-      <c r="S103" t="s">
+      <c r="S103" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="T103" t="s">
-        <v>43</v>
-      </c>
-      <c r="U103" t="s">
-        <v>43</v>
-      </c>
-      <c r="V103" t="s">
-        <v>43</v>
-      </c>
-      <c r="W103" t="s">
-        <v>43</v>
-      </c>
-      <c r="X103" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y103" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z103" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA103" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB103" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC103" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD103" t="s">
+      <c r="T103" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="U103" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="V103" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="W103" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X103" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y103" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z103" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA103" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB103" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC103" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD103" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="AE103" t="s">
+      <c r="AE103" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="104" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A104">
+    <row r="104" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="4">
         <v>103</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="C104" t="s">
+      <c r="C104" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="D104" t="s">
+      <c r="D104" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="E104" t="s">
+      <c r="E104" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F104">
+      <c r="F104" s="4">
         <v>2015</v>
       </c>
-      <c r="G104" t="s">
-        <v>43</v>
-      </c>
-      <c r="H104" s="3" t="s">
+      <c r="G104" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H104" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="I104" t="s">
+      <c r="I104" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="J104" t="s">
+      <c r="J104" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K104" t="s">
+      <c r="K104" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="L104" t="s">
+      <c r="L104" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M104" s="1">
+      <c r="M104" s="6">
         <v>42162</v>
       </c>
-      <c r="N104">
+      <c r="N104" s="4">
         <v>47.222833333333298</v>
       </c>
-      <c r="O104">
+      <c r="O104" s="4">
         <v>-122.810666666667</v>
       </c>
-      <c r="P104" t="s">
+      <c r="P104" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="Q104" t="s">
-        <v>40</v>
-      </c>
-      <c r="R104">
+      <c r="Q104" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="R104" s="4">
         <v>-1.7678400000000001</v>
       </c>
-      <c r="S104" t="s">
+      <c r="S104" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="T104" t="s">
-        <v>43</v>
-      </c>
-      <c r="U104" t="s">
-        <v>43</v>
-      </c>
-      <c r="V104" t="s">
-        <v>43</v>
-      </c>
-      <c r="W104" t="s">
-        <v>43</v>
-      </c>
-      <c r="X104" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y104" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z104" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA104" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB104" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC104" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD104" t="s">
+      <c r="T104" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="U104" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="V104" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="W104" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X104" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y104" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z104" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA104" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB104" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC104" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD104" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="AE104" t="s">
+      <c r="AE104" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="105" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>104</v>
       </c>
@@ -13039,7 +13040,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="106" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>105</v>
       </c>
@@ -13134,7 +13135,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="107" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>106</v>
       </c>
@@ -13229,7 +13230,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="108" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>107</v>
       </c>
@@ -13324,7 +13325,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="109" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>108</v>
       </c>
@@ -13419,7 +13420,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="110" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>109</v>
       </c>
@@ -13514,7 +13515,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="111" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>110</v>
       </c>
@@ -13609,7 +13610,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="112" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>111</v>
       </c>
@@ -13704,7 +13705,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="113" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>112</v>
       </c>
@@ -13799,7 +13800,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="114" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>113</v>
       </c>
@@ -13894,7 +13895,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="115" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>114</v>
       </c>
@@ -13989,7 +13990,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="116" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>115</v>
       </c>
@@ -14084,7 +14085,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="117" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>116</v>
       </c>
@@ -14179,7 +14180,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="118" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>117</v>
       </c>
@@ -14274,7 +14275,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="119" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>118</v>
       </c>
@@ -14369,7 +14370,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="120" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>119</v>
       </c>
@@ -14464,7 +14465,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="121" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>120</v>
       </c>
@@ -14559,7 +14560,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="122" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>121</v>
       </c>
@@ -14654,7 +14655,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="123" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>122</v>
       </c>
@@ -14749,7 +14750,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="124" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>123</v>
       </c>
@@ -14844,7 +14845,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="125" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>124</v>
       </c>
@@ -14939,7 +14940,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="126" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>125</v>
       </c>
@@ -15034,7 +15035,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="127" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>126</v>
       </c>
@@ -15129,7 +15130,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="128" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>127</v>
       </c>
@@ -15224,7 +15225,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="129" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>128</v>
       </c>
@@ -15319,7 +15320,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="130" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>129</v>
       </c>
@@ -15414,7 +15415,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="131" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>130</v>
       </c>
@@ -15509,7 +15510,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="132" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>131</v>
       </c>
@@ -15604,7 +15605,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="133" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>132</v>
       </c>
@@ -15699,7 +15700,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="134" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>133</v>
       </c>
@@ -15794,7 +15795,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="135" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>134</v>
       </c>
@@ -15889,7 +15890,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="136" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>135</v>
       </c>
@@ -15984,7 +15985,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="137" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>136</v>
       </c>
@@ -16079,7 +16080,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="138" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>137</v>
       </c>
@@ -16174,7 +16175,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="139" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>138</v>
       </c>
@@ -16269,7 +16270,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="140" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>139</v>
       </c>
@@ -16364,7 +16365,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="141" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>140</v>
       </c>
@@ -16459,7 +16460,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="142" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>141</v>
       </c>
@@ -16554,7 +16555,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="143" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>142</v>
       </c>
@@ -16649,7 +16650,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="144" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>143</v>
       </c>
@@ -16744,7 +16745,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="145" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>144</v>
       </c>
@@ -16839,7 +16840,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="146" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>145</v>
       </c>
@@ -16934,7 +16935,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="147" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>146</v>
       </c>
@@ -17029,7 +17030,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="148" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>147</v>
       </c>
@@ -17124,7 +17125,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="149" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>148</v>
       </c>
@@ -17219,7 +17220,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="150" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>149</v>
       </c>
@@ -17314,7 +17315,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="151" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>150</v>
       </c>
@@ -17409,7 +17410,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="152" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>151</v>
       </c>
@@ -17504,7 +17505,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="153" spans="1:31" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="4">
         <v>152</v>
       </c>
@@ -17599,7 +17600,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="154" spans="1:31" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="4">
         <v>153</v>
       </c>
@@ -17694,7 +17695,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="155" spans="1:31" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="4">
         <v>154</v>
       </c>
@@ -17789,7 +17790,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="156" spans="1:31" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="4">
         <v>155</v>
       </c>
@@ -17884,1147 +17885,1147 @@
         <v>163</v>
       </c>
     </row>
-    <row r="157" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="10">
+    <row r="157" spans="1:31" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="7">
         <v>156</v>
       </c>
-      <c r="B157" s="10" t="s">
+      <c r="B157" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="C157" s="10" t="s">
+      <c r="C157" s="7" t="s">
         <v>407</v>
       </c>
-      <c r="D157" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E157" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F157" s="10">
+      <c r="D157" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E157" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F157" s="7">
         <v>2017</v>
       </c>
-      <c r="G157" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H157" s="11" t="s">
+      <c r="G157" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H157" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="I157" s="10" t="s">
+      <c r="I157" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="J157" s="10" t="s">
+      <c r="J157" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="K157" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="L157" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="M157" s="12">
+      <c r="K157" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="L157" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M157" s="9">
         <v>42854</v>
       </c>
-      <c r="N157" s="10">
+      <c r="N157" s="7">
         <v>47.222461000000003</v>
       </c>
-      <c r="O157" s="10">
+      <c r="O157" s="7">
         <v>-122.810239</v>
       </c>
-      <c r="P157" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q157" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="R157" s="10">
+      <c r="P157" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q157" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="R157" s="7">
         <v>-1.1000000000000001</v>
       </c>
-      <c r="S157" s="10" t="s">
+      <c r="S157" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="T157" s="10">
+      <c r="T157" s="7">
         <v>1</v>
       </c>
-      <c r="U157" s="10">
+      <c r="U157" s="7">
         <v>1</v>
       </c>
-      <c r="V157" s="10">
+      <c r="V157" s="7">
         <v>1</v>
       </c>
-      <c r="W157" s="10">
+      <c r="W157" s="7">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="X157" s="10">
+      <c r="X157" s="7">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="Y157" s="10">
+      <c r="Y157" s="7">
         <v>3</v>
       </c>
-      <c r="Z157" s="10">
+      <c r="Z157" s="7">
         <v>12</v>
       </c>
-      <c r="AA157" s="10">
+      <c r="AA157" s="7">
         <v>12</v>
       </c>
-      <c r="AB157" s="10">
+      <c r="AB157" s="7">
         <v>1500</v>
       </c>
-      <c r="AC157" s="10" t="s">
+      <c r="AC157" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="AD157" s="10" t="s">
+      <c r="AD157" s="7" t="s">
         <v>408</v>
       </c>
-      <c r="AE157" s="10" t="s">
+      <c r="AE157" s="7" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="158" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="10">
+    <row r="158" spans="1:31" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="7">
         <v>157</v>
       </c>
-      <c r="B158" s="10" t="s">
+      <c r="B158" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="C158" s="10" t="s">
+      <c r="C158" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="D158" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E158" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F158" s="10">
+      <c r="D158" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E158" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F158" s="7">
         <v>2017</v>
       </c>
-      <c r="G158" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H158" s="11" t="s">
+      <c r="G158" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H158" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="I158" s="10" t="s">
+      <c r="I158" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="J158" s="10" t="s">
+      <c r="J158" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="K158" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="L158" s="10" t="s">
+      <c r="K158" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="L158" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="M158" s="12">
+      <c r="M158" s="9">
         <v>42854</v>
       </c>
-      <c r="N158" s="10">
+      <c r="N158" s="7">
         <v>47.222489000000003</v>
       </c>
-      <c r="O158" s="10">
+      <c r="O158" s="7">
         <v>-122.81026199999999</v>
       </c>
-      <c r="P158" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q158" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="R158" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="S158" s="10" t="s">
+      <c r="P158" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q158" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="R158" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="S158" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="T158" s="10">
+      <c r="T158" s="7">
         <v>1</v>
       </c>
-      <c r="U158" s="10">
+      <c r="U158" s="7">
         <v>1</v>
       </c>
-      <c r="V158" s="10">
+      <c r="V158" s="7">
         <v>1</v>
       </c>
-      <c r="W158" s="10">
+      <c r="W158" s="7">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="X158" s="10">
+      <c r="X158" s="7">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="Y158" s="10">
+      <c r="Y158" s="7">
         <v>3</v>
       </c>
-      <c r="Z158" s="10">
+      <c r="Z158" s="7">
         <v>12</v>
       </c>
-      <c r="AA158" s="10">
+      <c r="AA158" s="7">
         <v>12</v>
       </c>
-      <c r="AB158" s="10">
+      <c r="AB158" s="7">
         <v>1500</v>
       </c>
-      <c r="AC158" s="10" t="s">
+      <c r="AC158" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="AD158" s="10" t="s">
+      <c r="AD158" s="7" t="s">
         <v>408</v>
       </c>
-      <c r="AE158" s="10" t="s">
+      <c r="AE158" s="7" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="159" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="10">
+    <row r="159" spans="1:31" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="7">
         <v>158</v>
       </c>
-      <c r="B159" s="10" t="s">
+      <c r="B159" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="C159" s="10" t="s">
+      <c r="C159" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="D159" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E159" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F159" s="10">
+      <c r="D159" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E159" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F159" s="7">
         <v>2017</v>
       </c>
-      <c r="G159" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H159" s="11" t="s">
+      <c r="G159" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H159" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="I159" s="10" t="s">
+      <c r="I159" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="J159" s="10" t="s">
+      <c r="J159" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="K159" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="L159" s="10" t="s">
+      <c r="K159" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="L159" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="M159" s="12">
+      <c r="M159" s="9">
         <v>42854</v>
       </c>
-      <c r="N159" s="10">
+      <c r="N159" s="7">
         <v>47.222512000000002</v>
       </c>
-      <c r="O159" s="10">
+      <c r="O159" s="7">
         <v>-122.810267</v>
       </c>
-      <c r="P159" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q159" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="R159" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="S159" s="10" t="s">
+      <c r="P159" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q159" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="R159" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="S159" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="T159" s="10">
+      <c r="T159" s="7">
         <v>1</v>
       </c>
-      <c r="U159" s="10">
+      <c r="U159" s="7">
         <v>1</v>
       </c>
-      <c r="V159" s="10">
+      <c r="V159" s="7">
         <v>1</v>
       </c>
-      <c r="W159" s="10">
+      <c r="W159" s="7">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="X159" s="10">
+      <c r="X159" s="7">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="Y159" s="10">
+      <c r="Y159" s="7">
         <v>3</v>
       </c>
-      <c r="Z159" s="10">
+      <c r="Z159" s="7">
         <v>12</v>
       </c>
-      <c r="AA159" s="10">
+      <c r="AA159" s="7">
         <v>12</v>
       </c>
-      <c r="AB159" s="10">
+      <c r="AB159" s="7">
         <v>1500</v>
       </c>
-      <c r="AC159" s="10" t="s">
+      <c r="AC159" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="AD159" s="10" t="s">
+      <c r="AD159" s="7" t="s">
         <v>408</v>
       </c>
-      <c r="AE159" s="10" t="s">
+      <c r="AE159" s="7" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="160" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="10">
+    <row r="160" spans="1:31" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="7">
         <v>159</v>
       </c>
-      <c r="B160" s="10" t="s">
+      <c r="B160" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="C160" s="10" t="s">
+      <c r="C160" s="7" t="s">
         <v>411</v>
       </c>
-      <c r="D160" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E160" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F160" s="10">
+      <c r="D160" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E160" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F160" s="7">
         <v>2017</v>
       </c>
-      <c r="G160" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H160" s="11" t="s">
+      <c r="G160" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H160" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="I160" s="10" t="s">
+      <c r="I160" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="J160" s="10" t="s">
+      <c r="J160" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="K160" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="L160" s="10" t="s">
+      <c r="K160" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="L160" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="M160" s="12">
+      <c r="M160" s="9">
         <v>42854</v>
       </c>
-      <c r="N160" s="10">
+      <c r="N160" s="7">
         <v>47.222541999999997</v>
       </c>
-      <c r="O160" s="10">
+      <c r="O160" s="7">
         <v>-122.81027899999999</v>
       </c>
-      <c r="P160" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q160" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="R160" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="S160" s="10" t="s">
+      <c r="P160" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q160" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="R160" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="S160" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="T160" s="10">
+      <c r="T160" s="7">
         <v>1</v>
       </c>
-      <c r="U160" s="10">
+      <c r="U160" s="7">
         <v>1</v>
       </c>
-      <c r="V160" s="10">
+      <c r="V160" s="7">
         <v>1</v>
       </c>
-      <c r="W160" s="10">
+      <c r="W160" s="7">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="X160" s="10">
+      <c r="X160" s="7">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="Y160" s="10">
+      <c r="Y160" s="7">
         <v>3</v>
       </c>
-      <c r="Z160" s="10">
+      <c r="Z160" s="7">
         <v>12</v>
       </c>
-      <c r="AA160" s="10">
+      <c r="AA160" s="7">
         <v>12</v>
       </c>
-      <c r="AB160" s="10">
+      <c r="AB160" s="7">
         <v>1500</v>
       </c>
-      <c r="AC160" s="10" t="s">
+      <c r="AC160" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="AD160" s="10" t="s">
+      <c r="AD160" s="7" t="s">
         <v>408</v>
       </c>
-      <c r="AE160" s="10" t="s">
+      <c r="AE160" s="7" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="161" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="10">
+    <row r="161" spans="1:31" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="7">
         <v>160</v>
       </c>
-      <c r="B161" s="10" t="s">
+      <c r="B161" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="C161" s="10" t="s">
+      <c r="C161" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="D161" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E161" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F161" s="10">
+      <c r="D161" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E161" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F161" s="7">
         <v>2017</v>
       </c>
-      <c r="G161" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H161" s="11" t="s">
+      <c r="G161" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H161" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="I161" s="10" t="s">
+      <c r="I161" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="J161" s="10" t="s">
+      <c r="J161" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="K161" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="L161" s="10" t="s">
+      <c r="K161" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="L161" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="M161" s="12">
+      <c r="M161" s="9">
         <v>42854</v>
       </c>
-      <c r="N161" s="10">
+      <c r="N161" s="7">
         <v>47.222552</v>
       </c>
-      <c r="O161" s="10">
+      <c r="O161" s="7">
         <v>-122.810293</v>
       </c>
-      <c r="P161" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q161" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="R161" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="S161" s="10" t="s">
+      <c r="P161" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q161" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="R161" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="S161" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="T161" s="10">
+      <c r="T161" s="7">
         <v>1</v>
       </c>
-      <c r="U161" s="10">
+      <c r="U161" s="7">
         <v>1</v>
       </c>
-      <c r="V161" s="10">
+      <c r="V161" s="7">
         <v>1</v>
       </c>
-      <c r="W161" s="10">
+      <c r="W161" s="7">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="X161" s="10">
+      <c r="X161" s="7">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="Y161" s="10">
+      <c r="Y161" s="7">
         <v>3</v>
       </c>
-      <c r="Z161" s="10">
+      <c r="Z161" s="7">
         <v>12</v>
       </c>
-      <c r="AA161" s="10">
+      <c r="AA161" s="7">
         <v>12</v>
       </c>
-      <c r="AB161" s="10">
+      <c r="AB161" s="7">
         <v>1500</v>
       </c>
-      <c r="AC161" s="10" t="s">
+      <c r="AC161" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="AD161" s="10" t="s">
+      <c r="AD161" s="7" t="s">
         <v>408</v>
       </c>
-      <c r="AE161" s="10" t="s">
+      <c r="AE161" s="7" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="162" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="10">
+    <row r="162" spans="1:31" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="7">
         <v>161</v>
       </c>
-      <c r="B162" s="10" t="s">
+      <c r="B162" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="C162" s="10" t="s">
+      <c r="C162" s="7" t="s">
         <v>413</v>
       </c>
-      <c r="D162" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E162" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F162" s="10">
+      <c r="D162" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E162" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F162" s="7">
         <v>2017</v>
       </c>
-      <c r="G162" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H162" s="11" t="s">
+      <c r="G162" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H162" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="I162" s="10" t="s">
+      <c r="I162" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="J162" s="10" t="s">
+      <c r="J162" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="K162" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="L162" s="10" t="s">
+      <c r="K162" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="L162" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="M162" s="12">
+      <c r="M162" s="9">
         <v>42854</v>
       </c>
-      <c r="N162" s="10">
+      <c r="N162" s="7">
         <v>47.222596000000003</v>
       </c>
-      <c r="O162" s="10">
+      <c r="O162" s="7">
         <v>-122.810309</v>
       </c>
-      <c r="P162" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q162" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="R162" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="S162" s="10" t="s">
+      <c r="P162" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q162" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="R162" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="S162" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="T162" s="10">
+      <c r="T162" s="7">
         <v>1</v>
       </c>
-      <c r="U162" s="10">
+      <c r="U162" s="7">
         <v>1</v>
       </c>
-      <c r="V162" s="10">
+      <c r="V162" s="7">
         <v>1</v>
       </c>
-      <c r="W162" s="10">
+      <c r="W162" s="7">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="X162" s="10">
+      <c r="X162" s="7">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="Y162" s="10">
+      <c r="Y162" s="7">
         <v>3</v>
       </c>
-      <c r="Z162" s="10">
+      <c r="Z162" s="7">
         <v>12</v>
       </c>
-      <c r="AA162" s="10">
+      <c r="AA162" s="7">
         <v>12</v>
       </c>
-      <c r="AB162" s="10">
+      <c r="AB162" s="7">
         <v>1500</v>
       </c>
-      <c r="AC162" s="10" t="s">
+      <c r="AC162" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="AD162" s="10" t="s">
+      <c r="AD162" s="7" t="s">
         <v>408</v>
       </c>
-      <c r="AE162" s="10" t="s">
+      <c r="AE162" s="7" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="163" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="10">
+    <row r="163" spans="1:31" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="7">
         <v>162</v>
       </c>
-      <c r="B163" s="10" t="s">
+      <c r="B163" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="C163" s="10" t="s">
+      <c r="C163" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="D163" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E163" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F163" s="10">
+      <c r="D163" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E163" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F163" s="7">
         <v>2017</v>
       </c>
-      <c r="G163" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H163" s="11" t="s">
+      <c r="G163" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H163" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="I163" s="10" t="s">
+      <c r="I163" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="J163" s="10" t="s">
+      <c r="J163" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="K163" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="L163" s="10" t="s">
+      <c r="K163" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="L163" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="M163" s="12">
+      <c r="M163" s="9">
         <v>42854</v>
       </c>
-      <c r="N163" s="10">
+      <c r="N163" s="7">
         <v>47.222611999999998</v>
       </c>
-      <c r="O163" s="10">
+      <c r="O163" s="7">
         <v>-122.810312</v>
       </c>
-      <c r="P163" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q163" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="R163" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="S163" s="10" t="s">
+      <c r="P163" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q163" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="R163" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="S163" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="T163" s="10">
+      <c r="T163" s="7">
         <v>1</v>
       </c>
-      <c r="U163" s="10">
+      <c r="U163" s="7">
         <v>1</v>
       </c>
-      <c r="V163" s="10">
+      <c r="V163" s="7">
         <v>1</v>
       </c>
-      <c r="W163" s="10">
+      <c r="W163" s="7">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="X163" s="10">
+      <c r="X163" s="7">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="Y163" s="10">
+      <c r="Y163" s="7">
         <v>3</v>
       </c>
-      <c r="Z163" s="10">
+      <c r="Z163" s="7">
         <v>12</v>
       </c>
-      <c r="AA163" s="10">
+      <c r="AA163" s="7">
         <v>12</v>
       </c>
-      <c r="AB163" s="10">
+      <c r="AB163" s="7">
         <v>1500</v>
       </c>
-      <c r="AC163" s="10" t="s">
+      <c r="AC163" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="AD163" s="10" t="s">
+      <c r="AD163" s="7" t="s">
         <v>408</v>
       </c>
-      <c r="AE163" s="10" t="s">
+      <c r="AE163" s="7" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="164" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="10">
+    <row r="164" spans="1:31" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="7">
         <v>163</v>
       </c>
-      <c r="B164" s="10" t="s">
+      <c r="B164" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="C164" s="10" t="s">
+      <c r="C164" s="7" t="s">
         <v>415</v>
       </c>
-      <c r="D164" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E164" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F164" s="10">
+      <c r="D164" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E164" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F164" s="7">
         <v>2017</v>
       </c>
-      <c r="G164" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H164" s="11" t="s">
+      <c r="G164" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H164" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="I164" s="10" t="s">
+      <c r="I164" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="J164" s="10" t="s">
+      <c r="J164" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="K164" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="L164" s="10" t="s">
+      <c r="K164" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="L164" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="M164" s="12">
+      <c r="M164" s="9">
         <v>42854</v>
       </c>
-      <c r="N164" s="10">
+      <c r="N164" s="7">
         <v>47.222638000000003</v>
       </c>
-      <c r="O164" s="10">
+      <c r="O164" s="7">
         <v>-122.810339</v>
       </c>
-      <c r="P164" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q164" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="R164" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="S164" s="10" t="s">
+      <c r="P164" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q164" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="R164" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="S164" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="T164" s="10">
+      <c r="T164" s="7">
         <v>1</v>
       </c>
-      <c r="U164" s="10">
+      <c r="U164" s="7">
         <v>1</v>
       </c>
-      <c r="V164" s="10">
+      <c r="V164" s="7">
         <v>1</v>
       </c>
-      <c r="W164" s="10">
+      <c r="W164" s="7">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="X164" s="10">
+      <c r="X164" s="7">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="Y164" s="10">
+      <c r="Y164" s="7">
         <v>3</v>
       </c>
-      <c r="Z164" s="10">
+      <c r="Z164" s="7">
         <v>12</v>
       </c>
-      <c r="AA164" s="10">
+      <c r="AA164" s="7">
         <v>12</v>
       </c>
-      <c r="AB164" s="10">
+      <c r="AB164" s="7">
         <v>1500</v>
       </c>
-      <c r="AC164" s="10" t="s">
+      <c r="AC164" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="AD164" s="10" t="s">
+      <c r="AD164" s="7" t="s">
         <v>408</v>
       </c>
-      <c r="AE164" s="10" t="s">
+      <c r="AE164" s="7" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="165" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="10">
+    <row r="165" spans="1:31" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="7">
         <v>164</v>
       </c>
-      <c r="B165" s="10" t="s">
+      <c r="B165" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="C165" s="10" t="s">
+      <c r="C165" s="7" t="s">
         <v>416</v>
       </c>
-      <c r="D165" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E165" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F165" s="10">
+      <c r="D165" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E165" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F165" s="7">
         <v>2017</v>
       </c>
-      <c r="G165" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H165" s="11" t="s">
+      <c r="G165" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H165" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="I165" s="10" t="s">
+      <c r="I165" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="J165" s="10" t="s">
+      <c r="J165" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="K165" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="L165" s="10" t="s">
+      <c r="K165" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="L165" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="M165" s="12">
+      <c r="M165" s="9">
         <v>42854</v>
       </c>
-      <c r="N165" s="10">
+      <c r="N165" s="7">
         <v>47.222659</v>
       </c>
-      <c r="O165" s="10">
+      <c r="O165" s="7">
         <v>-122.810361</v>
       </c>
-      <c r="P165" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q165" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="R165" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="S165" s="10" t="s">
+      <c r="P165" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q165" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="R165" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="S165" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="T165" s="10">
+      <c r="T165" s="7">
         <v>1</v>
       </c>
-      <c r="U165" s="10">
+      <c r="U165" s="7">
         <v>1</v>
       </c>
-      <c r="V165" s="10">
+      <c r="V165" s="7">
         <v>1</v>
       </c>
-      <c r="W165" s="10">
+      <c r="W165" s="7">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="X165" s="10">
+      <c r="X165" s="7">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="Y165" s="10">
+      <c r="Y165" s="7">
         <v>3</v>
       </c>
-      <c r="Z165" s="10">
+      <c r="Z165" s="7">
         <v>12</v>
       </c>
-      <c r="AA165" s="10">
+      <c r="AA165" s="7">
         <v>12</v>
       </c>
-      <c r="AB165" s="10">
+      <c r="AB165" s="7">
         <v>1500</v>
       </c>
-      <c r="AC165" s="10" t="s">
+      <c r="AC165" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="AD165" s="10" t="s">
+      <c r="AD165" s="7" t="s">
         <v>408</v>
       </c>
-      <c r="AE165" s="10" t="s">
+      <c r="AE165" s="7" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="166" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="10">
+    <row r="166" spans="1:31" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="7">
         <v>165</v>
       </c>
-      <c r="B166" s="10" t="s">
+      <c r="B166" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="C166" s="10" t="s">
+      <c r="C166" s="7" t="s">
         <v>417</v>
       </c>
-      <c r="D166" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E166" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F166" s="10">
+      <c r="D166" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E166" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F166" s="7">
         <v>2017</v>
       </c>
-      <c r="G166" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H166" s="11" t="s">
+      <c r="G166" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H166" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="I166" s="10" t="s">
+      <c r="I166" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="J166" s="10" t="s">
+      <c r="J166" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="K166" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="L166" s="10" t="s">
+      <c r="K166" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="L166" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="M166" s="12">
+      <c r="M166" s="9">
         <v>42854</v>
       </c>
-      <c r="N166" s="10">
+      <c r="N166" s="7">
         <v>47.222687999999998</v>
       </c>
-      <c r="O166" s="10">
+      <c r="O166" s="7">
         <v>-122.810372</v>
       </c>
-      <c r="P166" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q166" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="R166" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="S166" s="10" t="s">
+      <c r="P166" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q166" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="R166" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="S166" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="T166" s="10">
+      <c r="T166" s="7">
         <v>1</v>
       </c>
-      <c r="U166" s="10">
+      <c r="U166" s="7">
         <v>1</v>
       </c>
-      <c r="V166" s="10">
+      <c r="V166" s="7">
         <v>1</v>
       </c>
-      <c r="W166" s="10">
+      <c r="W166" s="7">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="X166" s="10">
+      <c r="X166" s="7">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="Y166" s="10">
+      <c r="Y166" s="7">
         <v>3</v>
       </c>
-      <c r="Z166" s="10">
+      <c r="Z166" s="7">
         <v>12</v>
       </c>
-      <c r="AA166" s="10">
+      <c r="AA166" s="7">
         <v>12</v>
       </c>
-      <c r="AB166" s="10">
+      <c r="AB166" s="7">
         <v>1500</v>
       </c>
-      <c r="AC166" s="10" t="s">
+      <c r="AC166" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="AD166" s="10" t="s">
+      <c r="AD166" s="7" t="s">
         <v>408</v>
       </c>
-      <c r="AE166" s="10" t="s">
+      <c r="AE166" s="7" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="167" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="10">
+    <row r="167" spans="1:31" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="7">
         <v>166</v>
       </c>
-      <c r="B167" s="10" t="s">
+      <c r="B167" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="C167" s="10" t="s">
+      <c r="C167" s="7" t="s">
         <v>418</v>
       </c>
-      <c r="D167" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E167" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F167" s="10">
+      <c r="D167" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E167" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F167" s="7">
         <v>2017</v>
       </c>
-      <c r="G167" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H167" s="11" t="s">
+      <c r="G167" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H167" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="I167" s="10" t="s">
+      <c r="I167" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="J167" s="10" t="s">
+      <c r="J167" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="K167" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="L167" s="10" t="s">
+      <c r="K167" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="L167" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="M167" s="12">
+      <c r="M167" s="9">
         <v>42854</v>
       </c>
-      <c r="N167" s="10">
+      <c r="N167" s="7">
         <v>47.222720000000002</v>
       </c>
-      <c r="O167" s="10">
+      <c r="O167" s="7">
         <v>-122.81038599999999</v>
       </c>
-      <c r="P167" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q167" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="R167" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="S167" s="10" t="s">
+      <c r="P167" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q167" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="R167" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="S167" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="T167" s="10">
+      <c r="T167" s="7">
         <v>1</v>
       </c>
-      <c r="U167" s="10">
+      <c r="U167" s="7">
         <v>1</v>
       </c>
-      <c r="V167" s="10">
+      <c r="V167" s="7">
         <v>1</v>
       </c>
-      <c r="W167" s="10">
+      <c r="W167" s="7">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="X167" s="10">
+      <c r="X167" s="7">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="Y167" s="10">
+      <c r="Y167" s="7">
         <v>3</v>
       </c>
-      <c r="Z167" s="10">
+      <c r="Z167" s="7">
         <v>12</v>
       </c>
-      <c r="AA167" s="10">
+      <c r="AA167" s="7">
         <v>12</v>
       </c>
-      <c r="AB167" s="10">
+      <c r="AB167" s="7">
         <v>1500</v>
       </c>
-      <c r="AC167" s="10" t="s">
+      <c r="AC167" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="AD167" s="10" t="s">
+      <c r="AD167" s="7" t="s">
         <v>408</v>
       </c>
-      <c r="AE167" s="10" t="s">
+      <c r="AE167" s="7" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="168" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="10">
+    <row r="168" spans="1:31" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="7">
         <v>167</v>
       </c>
-      <c r="B168" s="10" t="s">
+      <c r="B168" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="C168" s="10" t="s">
+      <c r="C168" s="7" t="s">
         <v>419</v>
       </c>
-      <c r="D168" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E168" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F168" s="10">
+      <c r="D168" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E168" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F168" s="7">
         <v>2017</v>
       </c>
-      <c r="G168" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H168" s="11" t="s">
+      <c r="G168" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H168" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="I168" s="10" t="s">
+      <c r="I168" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="J168" s="10" t="s">
+      <c r="J168" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="K168" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="L168" s="10" t="s">
+      <c r="K168" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="L168" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="M168" s="12">
+      <c r="M168" s="9">
         <v>42854</v>
       </c>
-      <c r="N168" s="10">
+      <c r="N168" s="7">
         <v>47.222732999999998</v>
       </c>
-      <c r="O168" s="10">
+      <c r="O168" s="7">
         <v>-122.8104</v>
       </c>
-      <c r="P168" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q168" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="R168" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="S168" s="10" t="s">
+      <c r="P168" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q168" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="R168" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="S168" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="T168" s="10">
+      <c r="T168" s="7">
         <v>1</v>
       </c>
-      <c r="U168" s="10">
+      <c r="U168" s="7">
         <v>1</v>
       </c>
-      <c r="V168" s="10">
+      <c r="V168" s="7">
         <v>1</v>
       </c>
-      <c r="W168" s="10">
+      <c r="W168" s="7">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="X168" s="10">
+      <c r="X168" s="7">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="Y168" s="10">
+      <c r="Y168" s="7">
         <v>3</v>
       </c>
-      <c r="Z168" s="10">
+      <c r="Z168" s="7">
         <v>12</v>
       </c>
-      <c r="AA168" s="10">
+      <c r="AA168" s="7">
         <v>12</v>
       </c>
-      <c r="AB168" s="10">
+      <c r="AB168" s="7">
         <v>1500</v>
       </c>
-      <c r="AC168" s="10" t="s">
+      <c r="AC168" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="AD168" s="10" t="s">
+      <c r="AD168" s="7" t="s">
         <v>408</v>
       </c>
-      <c r="AE168" s="10" t="s">
+      <c r="AE168" s="7" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="169" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>168</v>
       </c>
@@ -19119,7 +19120,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="170" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>169</v>
       </c>
@@ -19214,7 +19215,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="171" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>170</v>
       </c>
@@ -19309,7 +19310,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="172" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>171</v>
       </c>
@@ -19404,7 +19405,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="173" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>172</v>
       </c>
@@ -19499,7 +19500,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="174" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>173</v>
       </c>
@@ -19594,7 +19595,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="175" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>174</v>
       </c>
@@ -19689,7 +19690,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="176" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>175</v>
       </c>
@@ -19784,7 +19785,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="177" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>176</v>
       </c>
@@ -19879,7 +19880,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="178" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>177</v>
       </c>
@@ -19974,7 +19975,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="179" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>178</v>
       </c>
@@ -20069,7 +20070,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="180" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>179</v>
       </c>
@@ -20164,7 +20165,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="181" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>180</v>
       </c>
@@ -20259,7 +20260,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="182" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>181</v>
       </c>
@@ -20354,7 +20355,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="183" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>182</v>
       </c>
@@ -20449,7 +20450,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="184" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>183</v>
       </c>
@@ -20544,7 +20545,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="185" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>184</v>
       </c>
@@ -20639,7 +20640,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="186" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>185</v>
       </c>
@@ -20734,7 +20735,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="187" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>186</v>
       </c>
@@ -20829,7 +20830,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="188" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>187</v>
       </c>
@@ -20924,7 +20925,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="189" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>188</v>
       </c>
@@ -21019,7 +21020,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="190" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>189</v>
       </c>
@@ -21114,7 +21115,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="191" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>190</v>
       </c>
@@ -21209,7 +21210,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="192" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>191</v>
       </c>
@@ -21304,7 +21305,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="193" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>192</v>
       </c>
@@ -21399,7 +21400,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="194" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>193</v>
       </c>
@@ -21494,7 +21495,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="195" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>194</v>
       </c>
@@ -21589,7 +21590,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="196" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>195</v>
       </c>
@@ -21684,7 +21685,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="197" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>196</v>
       </c>
@@ -21779,7 +21780,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="198" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>197</v>
       </c>
@@ -21874,7 +21875,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="199" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>198</v>
       </c>
@@ -21969,7 +21970,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="200" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>199</v>
       </c>
@@ -22064,7 +22065,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="201" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>200</v>
       </c>
@@ -22159,7 +22160,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="202" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>201</v>
       </c>
@@ -22254,7 +22255,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="203" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>202</v>
       </c>
@@ -22349,7 +22350,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="204" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>203</v>
       </c>
@@ -22444,7 +22445,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="205" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>204</v>
       </c>
@@ -22539,7 +22540,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="206" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>205</v>
       </c>
@@ -22634,7 +22635,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="207" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>206</v>
       </c>
@@ -22729,7 +22730,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="208" spans="1:31" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="4">
         <v>207</v>
       </c>
@@ -22824,7 +22825,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="209" spans="1:31" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="4">
         <v>208</v>
       </c>
@@ -22919,197 +22920,197 @@
         <v>183</v>
       </c>
     </row>
-    <row r="210" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A210" s="10">
+    <row r="210" spans="1:31" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A210" s="7">
         <v>209</v>
       </c>
-      <c r="B210" s="10" t="s">
+      <c r="B210" s="7" t="s">
         <v>514</v>
       </c>
-      <c r="C210" s="10" t="s">
+      <c r="C210" s="7" t="s">
         <v>521</v>
       </c>
-      <c r="D210" s="10" t="s">
+      <c r="D210" s="7" t="s">
         <v>522</v>
       </c>
-      <c r="E210" s="10" t="s">
+      <c r="E210" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="F210" s="10">
+      <c r="F210" s="7">
         <v>2022</v>
       </c>
-      <c r="G210" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H210" s="11" t="s">
+      <c r="G210" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H210" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="I210" s="10" t="s">
+      <c r="I210" s="7" t="s">
         <v>517</v>
       </c>
-      <c r="J210" s="10" t="s">
+      <c r="J210" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="K210" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="L210" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="M210" s="12">
+      <c r="K210" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="L210" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M210" s="9">
         <v>44698</v>
       </c>
-      <c r="N210" s="10">
+      <c r="N210" s="7">
         <v>47.620460000000001</v>
       </c>
-      <c r="O210" s="10">
+      <c r="O210" s="7">
         <v>-122.36398</v>
       </c>
-      <c r="P210" s="10" t="s">
+      <c r="P210" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="Q210" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="R210" s="10">
+      <c r="Q210" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="R210" s="7">
         <v>-1.5</v>
       </c>
-      <c r="S210" s="10" t="s">
+      <c r="S210" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="T210" s="10">
+      <c r="T210" s="7">
         <v>1</v>
       </c>
-      <c r="U210" s="10">
+      <c r="U210" s="7">
         <v>0.5</v>
       </c>
-      <c r="V210" s="10">
+      <c r="V210" s="7">
         <v>0.5</v>
       </c>
-      <c r="W210" s="10">
+      <c r="W210" s="7">
         <v>1.5</v>
       </c>
-      <c r="X210" s="10">
+      <c r="X210" s="7">
         <v>0.15</v>
       </c>
-      <c r="Y210" s="10">
+      <c r="Y210" s="7">
         <v>6</v>
       </c>
-      <c r="Z210" s="10">
+      <c r="Z210" s="7">
         <v>120</v>
       </c>
-      <c r="AA210" s="10">
+      <c r="AA210" s="7">
         <v>240</v>
       </c>
-      <c r="AB210" s="10">
+      <c r="AB210" s="7">
         <v>80</v>
       </c>
-      <c r="AC210" s="10" t="s">
+      <c r="AC210" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="AD210" s="10" t="s">
+      <c r="AD210" s="7" t="s">
         <v>523</v>
       </c>
-      <c r="AE210" s="10" t="s">
+      <c r="AE210" s="7" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="211" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A211" s="10">
+    <row r="211" spans="1:31" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A211" s="7">
         <v>210</v>
       </c>
-      <c r="B211" s="10" t="s">
+      <c r="B211" s="7" t="s">
         <v>514</v>
       </c>
-      <c r="C211" s="10" t="s">
+      <c r="C211" s="7" t="s">
         <v>524</v>
       </c>
-      <c r="D211" s="10" t="s">
+      <c r="D211" s="7" t="s">
         <v>522</v>
       </c>
-      <c r="E211" s="10" t="s">
+      <c r="E211" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="F211" s="10">
+      <c r="F211" s="7">
         <v>2022</v>
       </c>
-      <c r="G211" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H211" s="11" t="s">
+      <c r="G211" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H211" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="I211" s="10" t="s">
+      <c r="I211" s="7" t="s">
         <v>517</v>
       </c>
-      <c r="J211" s="10" t="s">
+      <c r="J211" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="K211" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="L211" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="M211" s="12">
+      <c r="K211" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="L211" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M211" s="9">
         <v>44698</v>
       </c>
-      <c r="N211" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="O211" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="P211" s="10" t="s">
+      <c r="N211" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="O211" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="P211" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="Q211" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="R211" s="10">
+      <c r="Q211" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="R211" s="7">
         <v>-1.6</v>
       </c>
-      <c r="S211" s="10" t="s">
+      <c r="S211" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="T211" s="10">
+      <c r="T211" s="7">
         <v>2.5</v>
       </c>
-      <c r="U211" s="10">
+      <c r="U211" s="7">
         <v>1</v>
       </c>
-      <c r="V211" s="10">
+      <c r="V211" s="7">
         <v>2.5</v>
       </c>
-      <c r="W211" s="10">
+      <c r="W211" s="7">
         <v>7.75</v>
       </c>
-      <c r="X211" s="10">
+      <c r="X211" s="7">
         <v>0.77500000000000002</v>
       </c>
-      <c r="Y211" s="10">
+      <c r="Y211" s="7">
         <v>31</v>
       </c>
-      <c r="Z211" s="10">
+      <c r="Z211" s="7">
         <v>620</v>
       </c>
-      <c r="AA211" s="10">
+      <c r="AA211" s="7">
         <v>248</v>
       </c>
-      <c r="AB211" s="10">
+      <c r="AB211" s="7">
         <v>80</v>
       </c>
-      <c r="AC211" s="10" t="s">
+      <c r="AC211" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="AD211" s="10" t="s">
+      <c r="AD211" s="7" t="s">
         <v>525</v>
       </c>
-      <c r="AE211" s="10" t="s">
+      <c r="AE211" s="7" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="212" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>211</v>
       </c>
@@ -23204,7 +23205,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="213" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>212</v>
       </c>
@@ -23299,7 +23300,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="214" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>213</v>
       </c>
@@ -23394,7 +23395,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="215" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>214</v>
       </c>
@@ -23489,7 +23490,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="216" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>215</v>
       </c>
@@ -23584,7 +23585,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="217" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>216</v>
       </c>
@@ -23679,7 +23680,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="218" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>217</v>
       </c>
@@ -23774,7 +23775,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="219" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>218</v>
       </c>
@@ -23869,7 +23870,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="220" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>219</v>
       </c>
@@ -23964,1527 +23965,1527 @@
         <v>543</v>
       </c>
     </row>
-    <row r="221" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A221">
+    <row r="221" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A221" s="4">
         <v>220</v>
       </c>
-      <c r="B221" t="s">
+      <c r="B221" s="4" t="s">
         <v>537</v>
       </c>
-      <c r="C221" t="s">
+      <c r="C221" s="4" t="s">
         <v>554</v>
       </c>
-      <c r="D221" t="s">
+      <c r="D221" s="4" t="s">
         <v>555</v>
       </c>
-      <c r="E221" t="s">
+      <c r="E221" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F221">
+      <c r="F221" s="4">
         <v>2015</v>
       </c>
-      <c r="G221" s="2" t="s">
+      <c r="G221" s="10" t="s">
         <v>540</v>
       </c>
-      <c r="H221" s="3" t="s">
+      <c r="H221" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="I221" t="s">
+      <c r="I221" s="4" t="s">
         <v>537</v>
       </c>
-      <c r="J221" t="s">
+      <c r="J221" s="4" t="s">
         <v>541</v>
       </c>
-      <c r="K221" t="s">
+      <c r="K221" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="L221" t="s">
+      <c r="L221" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="M221" s="1">
+      <c r="M221" s="6">
         <v>42095</v>
       </c>
-      <c r="N221">
+      <c r="N221" s="4">
         <v>47.823466666666697</v>
       </c>
-      <c r="O221">
+      <c r="O221" s="4">
         <v>-122.582033333333</v>
       </c>
-      <c r="P221" t="s">
+      <c r="P221" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="Q221" t="s">
-        <v>40</v>
-      </c>
-      <c r="R221" t="s">
-        <v>43</v>
-      </c>
-      <c r="S221" t="s">
+      <c r="Q221" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="R221" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="S221" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="T221">
+      <c r="T221" s="4">
         <v>48</v>
       </c>
-      <c r="U221">
+      <c r="U221" s="4">
         <v>36</v>
       </c>
-      <c r="V221">
+      <c r="V221" s="4">
         <v>1728</v>
       </c>
-      <c r="W221">
+      <c r="W221" s="4">
         <v>240</v>
       </c>
-      <c r="X221">
+      <c r="X221" s="4">
         <v>6</v>
       </c>
-      <c r="Y221">
+      <c r="Y221" s="4">
         <v>1200</v>
       </c>
-      <c r="Z221">
+      <c r="Z221" s="4">
         <v>4800</v>
       </c>
-      <c r="AA221">
+      <c r="AA221" s="4">
         <v>2.7777777777777799</v>
       </c>
-      <c r="AB221">
+      <c r="AB221" s="4">
         <v>20</v>
       </c>
-      <c r="AC221" t="s">
+      <c r="AC221" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="AD221" t="s">
-        <v>43</v>
-      </c>
-      <c r="AE221" t="s">
+      <c r="AD221" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE221" s="4" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="222" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A222">
+    <row r="222" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A222" s="4">
         <v>221</v>
       </c>
-      <c r="B222" t="s">
+      <c r="B222" s="4" t="s">
         <v>537</v>
       </c>
-      <c r="C222" t="s">
+      <c r="C222" s="4" t="s">
         <v>556</v>
       </c>
-      <c r="D222" t="s">
+      <c r="D222" s="4" t="s">
         <v>555</v>
       </c>
-      <c r="E222" t="s">
+      <c r="E222" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F222">
+      <c r="F222" s="4">
         <v>2015</v>
       </c>
-      <c r="G222" s="2" t="s">
+      <c r="G222" s="10" t="s">
         <v>540</v>
       </c>
-      <c r="H222" s="3" t="s">
+      <c r="H222" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="I222" t="s">
+      <c r="I222" s="4" t="s">
         <v>537</v>
       </c>
-      <c r="J222" t="s">
+      <c r="J222" s="4" t="s">
         <v>541</v>
       </c>
-      <c r="K222" t="s">
+      <c r="K222" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="L222" t="s">
+      <c r="L222" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M222" s="1">
+      <c r="M222" s="6">
         <v>42095</v>
       </c>
-      <c r="N222">
+      <c r="N222" s="4">
         <v>47.8232</v>
       </c>
-      <c r="O222">
+      <c r="O222" s="4">
         <v>-122.58154999999999</v>
       </c>
-      <c r="P222" t="s">
+      <c r="P222" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="Q222" t="s">
-        <v>40</v>
-      </c>
-      <c r="R222" t="s">
-        <v>43</v>
-      </c>
-      <c r="S222" t="s">
+      <c r="Q222" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="R222" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="S222" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="T222" t="s">
-        <v>43</v>
-      </c>
-      <c r="U222" t="s">
-        <v>43</v>
-      </c>
-      <c r="V222" t="s">
-        <v>43</v>
-      </c>
-      <c r="W222" t="s">
-        <v>43</v>
-      </c>
-      <c r="X222" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y222" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z222" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA222" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB222" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC222" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD222" t="s">
-        <v>43</v>
-      </c>
-      <c r="AE222" t="s">
+      <c r="T222" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="U222" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="V222" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="W222" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X222" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y222" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z222" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA222" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB222" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC222" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD222" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE222" s="4" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="223" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A223">
+    <row r="223" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A223" s="4">
         <v>222</v>
       </c>
-      <c r="B223" t="s">
+      <c r="B223" s="4" t="s">
         <v>537</v>
       </c>
-      <c r="C223" t="s">
+      <c r="C223" s="4" t="s">
         <v>557</v>
       </c>
-      <c r="D223" t="s">
+      <c r="D223" s="4" t="s">
         <v>555</v>
       </c>
-      <c r="E223" t="s">
+      <c r="E223" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F223">
+      <c r="F223" s="4">
         <v>2015</v>
       </c>
-      <c r="G223" s="2" t="s">
+      <c r="G223" s="10" t="s">
         <v>540</v>
       </c>
-      <c r="H223" s="3" t="s">
+      <c r="H223" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="I223" t="s">
+      <c r="I223" s="4" t="s">
         <v>537</v>
       </c>
-      <c r="J223" t="s">
+      <c r="J223" s="4" t="s">
         <v>541</v>
       </c>
-      <c r="K223" t="s">
+      <c r="K223" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="L223" t="s">
+      <c r="L223" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M223" s="1">
+      <c r="M223" s="6">
         <v>42095</v>
       </c>
-      <c r="N223">
+      <c r="N223" s="4">
         <v>47.823050000000002</v>
       </c>
-      <c r="O223">
+      <c r="O223" s="4">
         <v>-122.581883333333</v>
       </c>
-      <c r="P223" t="s">
+      <c r="P223" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="Q223" t="s">
-        <v>40</v>
-      </c>
-      <c r="R223" t="s">
-        <v>43</v>
-      </c>
-      <c r="S223" t="s">
+      <c r="Q223" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="R223" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="S223" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="T223" t="s">
-        <v>43</v>
-      </c>
-      <c r="U223" t="s">
-        <v>43</v>
-      </c>
-      <c r="V223" t="s">
-        <v>43</v>
-      </c>
-      <c r="W223" t="s">
-        <v>43</v>
-      </c>
-      <c r="X223" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y223" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z223" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA223" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB223" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC223" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD223" t="s">
-        <v>43</v>
-      </c>
-      <c r="AE223" t="s">
+      <c r="T223" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="U223" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="V223" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="W223" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X223" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y223" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z223" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA223" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB223" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC223" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD223" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE223" s="4" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="224" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A224">
+    <row r="224" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A224" s="4">
         <v>223</v>
       </c>
-      <c r="B224" t="s">
+      <c r="B224" s="4" t="s">
         <v>537</v>
       </c>
-      <c r="C224" t="s">
+      <c r="C224" s="4" t="s">
         <v>558</v>
       </c>
-      <c r="D224" t="s">
+      <c r="D224" s="4" t="s">
         <v>555</v>
       </c>
-      <c r="E224" t="s">
+      <c r="E224" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F224">
+      <c r="F224" s="4">
         <v>2015</v>
       </c>
-      <c r="G224" s="2" t="s">
+      <c r="G224" s="10" t="s">
         <v>540</v>
       </c>
-      <c r="H224" s="3" t="s">
+      <c r="H224" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="I224" t="s">
+      <c r="I224" s="4" t="s">
         <v>537</v>
       </c>
-      <c r="J224" t="s">
+      <c r="J224" s="4" t="s">
         <v>541</v>
       </c>
-      <c r="K224" t="s">
+      <c r="K224" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="L224" t="s">
+      <c r="L224" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M224" s="1">
+      <c r="M224" s="6">
         <v>42095</v>
       </c>
-      <c r="N224">
+      <c r="N224" s="4">
         <v>47.823283333333301</v>
       </c>
-      <c r="O224">
+      <c r="O224" s="4">
         <v>-122.58235000000001</v>
       </c>
-      <c r="P224" t="s">
+      <c r="P224" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="Q224" t="s">
-        <v>40</v>
-      </c>
-      <c r="R224">
+      <c r="Q224" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="R224" s="4">
         <v>-1.8288</v>
       </c>
-      <c r="S224" t="s">
+      <c r="S224" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="T224" t="s">
-        <v>43</v>
-      </c>
-      <c r="U224" t="s">
-        <v>43</v>
-      </c>
-      <c r="V224" t="s">
-        <v>43</v>
-      </c>
-      <c r="W224" t="s">
-        <v>43</v>
-      </c>
-      <c r="X224" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y224" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z224" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA224" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB224" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC224" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD224" t="s">
-        <v>43</v>
-      </c>
-      <c r="AE224" t="s">
+      <c r="T224" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="U224" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="V224" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="W224" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X224" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y224" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z224" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA224" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB224" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC224" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD224" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE224" s="4" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="225" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A225">
+    <row r="225" spans="1:31" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A225" s="7">
         <v>224</v>
       </c>
-      <c r="B225" t="s">
+      <c r="B225" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="C225" t="s">
+      <c r="C225" s="7" t="s">
         <v>559</v>
       </c>
-      <c r="D225" t="s">
+      <c r="D225" s="7" t="s">
         <v>560</v>
       </c>
-      <c r="E225" t="s">
+      <c r="E225" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="F225">
+      <c r="F225" s="7">
         <v>2015</v>
       </c>
-      <c r="G225" s="2" t="s">
+      <c r="G225" s="11" t="s">
         <v>540</v>
       </c>
-      <c r="H225" s="3" t="s">
+      <c r="H225" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="I225" t="s">
+      <c r="I225" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="J225" t="s">
+      <c r="J225" s="7" t="s">
         <v>541</v>
       </c>
-      <c r="K225" t="s">
+      <c r="K225" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="L225" t="s">
+      <c r="L225" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="M225" s="1">
+      <c r="M225" s="9">
         <v>42095</v>
       </c>
-      <c r="N225">
+      <c r="N225" s="7">
         <v>47.822049999999997</v>
       </c>
-      <c r="O225">
+      <c r="O225" s="7">
         <v>-122.5805</v>
       </c>
-      <c r="P225" t="s">
+      <c r="P225" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="Q225" t="s">
-        <v>40</v>
-      </c>
-      <c r="R225" t="s">
-        <v>43</v>
-      </c>
-      <c r="S225" t="s">
+      <c r="Q225" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="R225" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="S225" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="T225">
+      <c r="T225" s="7">
         <v>60</v>
       </c>
-      <c r="U225">
+      <c r="U225" s="7">
         <v>36</v>
       </c>
-      <c r="V225">
+      <c r="V225" s="7">
         <v>2160</v>
       </c>
-      <c r="W225">
+      <c r="W225" s="7">
         <v>320</v>
       </c>
-      <c r="X225">
+      <c r="X225" s="7">
         <v>7.9124999999999996</v>
       </c>
-      <c r="Y225">
+      <c r="Y225" s="7">
         <v>1582.5</v>
       </c>
-      <c r="Z225">
+      <c r="Z225" s="7">
         <v>6330</v>
       </c>
-      <c r="AA225">
+      <c r="AA225" s="7">
         <v>2.9305555555555598</v>
       </c>
-      <c r="AB225">
+      <c r="AB225" s="7">
         <v>19.78125</v>
       </c>
-      <c r="AC225" t="s">
+      <c r="AC225" s="7" t="s">
         <v>542</v>
       </c>
-      <c r="AD225" t="s">
-        <v>43</v>
-      </c>
-      <c r="AE225" t="s">
+      <c r="AD225" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE225" s="7" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="226" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A226">
+    <row r="226" spans="1:31" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A226" s="7">
         <v>225</v>
       </c>
-      <c r="B226" t="s">
+      <c r="B226" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="C226" t="s">
+      <c r="C226" s="7" t="s">
         <v>561</v>
       </c>
-      <c r="D226" t="s">
+      <c r="D226" s="7" t="s">
         <v>560</v>
       </c>
-      <c r="E226" t="s">
+      <c r="E226" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="F226">
+      <c r="F226" s="7">
         <v>2015</v>
       </c>
-      <c r="G226" s="2" t="s">
+      <c r="G226" s="11" t="s">
         <v>540</v>
       </c>
-      <c r="H226" s="3" t="s">
+      <c r="H226" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="I226" t="s">
+      <c r="I226" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="J226" t="s">
+      <c r="J226" s="7" t="s">
         <v>541</v>
       </c>
-      <c r="K226" t="s">
+      <c r="K226" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="L226" t="s">
+      <c r="L226" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="M226" s="1">
+      <c r="M226" s="9">
         <v>42095</v>
       </c>
-      <c r="N226">
+      <c r="N226" s="7">
         <v>47.821750000000002</v>
       </c>
-      <c r="O226">
+      <c r="O226" s="7">
         <v>-122.579966666667</v>
       </c>
-      <c r="P226" t="s">
+      <c r="P226" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="Q226" t="s">
-        <v>40</v>
-      </c>
-      <c r="R226" t="s">
-        <v>43</v>
-      </c>
-      <c r="S226" t="s">
+      <c r="Q226" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="R226" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="S226" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="T226" t="s">
-        <v>43</v>
-      </c>
-      <c r="U226" t="s">
-        <v>43</v>
-      </c>
-      <c r="V226" t="s">
-        <v>43</v>
-      </c>
-      <c r="W226" t="s">
-        <v>43</v>
-      </c>
-      <c r="X226" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y226" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z226" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA226" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB226" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC226" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD226" t="s">
-        <v>43</v>
-      </c>
-      <c r="AE226" t="s">
+      <c r="T226" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="U226" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="V226" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="W226" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X226" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y226" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z226" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA226" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB226" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC226" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD226" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE226" s="7" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="227" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A227">
+    <row r="227" spans="1:31" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A227" s="7">
         <v>226</v>
       </c>
-      <c r="B227" t="s">
+      <c r="B227" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="C227" t="s">
+      <c r="C227" s="7" t="s">
         <v>562</v>
       </c>
-      <c r="D227" t="s">
+      <c r="D227" s="7" t="s">
         <v>560</v>
       </c>
-      <c r="E227" t="s">
+      <c r="E227" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="F227">
+      <c r="F227" s="7">
         <v>2015</v>
       </c>
-      <c r="G227" s="2" t="s">
+      <c r="G227" s="11" t="s">
         <v>540</v>
       </c>
-      <c r="H227" s="3" t="s">
+      <c r="H227" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="I227" t="s">
+      <c r="I227" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="J227" t="s">
+      <c r="J227" s="7" t="s">
         <v>541</v>
       </c>
-      <c r="K227" t="s">
+      <c r="K227" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="L227" t="s">
+      <c r="L227" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="M227" s="1">
+      <c r="M227" s="9">
         <v>42095</v>
       </c>
-      <c r="N227">
+      <c r="N227" s="7">
         <v>47.821516666666703</v>
       </c>
-      <c r="O227">
+      <c r="O227" s="7">
         <v>-122.580216666667</v>
       </c>
-      <c r="P227" t="s">
+      <c r="P227" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="Q227" t="s">
-        <v>40</v>
-      </c>
-      <c r="R227" t="s">
-        <v>43</v>
-      </c>
-      <c r="S227" t="s">
+      <c r="Q227" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="R227" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="S227" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="T227" t="s">
-        <v>43</v>
-      </c>
-      <c r="U227" t="s">
-        <v>43</v>
-      </c>
-      <c r="V227" t="s">
-        <v>43</v>
-      </c>
-      <c r="W227" t="s">
-        <v>43</v>
-      </c>
-      <c r="X227" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y227" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z227" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA227" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB227" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC227" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD227" t="s">
-        <v>43</v>
-      </c>
-      <c r="AE227" t="s">
+      <c r="T227" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="U227" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="V227" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="W227" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X227" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y227" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z227" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA227" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB227" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC227" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD227" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE227" s="7" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="228" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A228">
+    <row r="228" spans="1:31" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A228" s="7">
         <v>227</v>
       </c>
-      <c r="B228" t="s">
+      <c r="B228" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="C228" t="s">
+      <c r="C228" s="7" t="s">
         <v>563</v>
       </c>
-      <c r="D228" t="s">
+      <c r="D228" s="7" t="s">
         <v>560</v>
       </c>
-      <c r="E228" t="s">
+      <c r="E228" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="F228">
+      <c r="F228" s="7">
         <v>2015</v>
       </c>
-      <c r="G228" s="2" t="s">
+      <c r="G228" s="11" t="s">
         <v>540</v>
       </c>
-      <c r="H228" s="3" t="s">
+      <c r="H228" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="I228" t="s">
+      <c r="I228" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="J228" t="s">
+      <c r="J228" s="7" t="s">
         <v>541</v>
       </c>
-      <c r="K228" t="s">
+      <c r="K228" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="L228" t="s">
+      <c r="L228" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="M228" s="1">
+      <c r="M228" s="9">
         <v>42095</v>
       </c>
-      <c r="N228">
+      <c r="N228" s="7">
         <v>47.8217833333333</v>
       </c>
-      <c r="O228">
+      <c r="O228" s="7">
         <v>-122.58091666666699</v>
       </c>
-      <c r="P228" t="s">
+      <c r="P228" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="Q228" t="s">
-        <v>40</v>
-      </c>
-      <c r="R228" t="s">
-        <v>43</v>
-      </c>
-      <c r="S228" t="s">
+      <c r="Q228" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="R228" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="S228" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="T228" t="s">
-        <v>43</v>
-      </c>
-      <c r="U228" t="s">
-        <v>43</v>
-      </c>
-      <c r="V228" t="s">
-        <v>43</v>
-      </c>
-      <c r="W228" t="s">
-        <v>43</v>
-      </c>
-      <c r="X228" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y228" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z228" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA228" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB228" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC228" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD228" t="s">
-        <v>43</v>
-      </c>
-      <c r="AE228" t="s">
+      <c r="T228" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="U228" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="V228" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="W228" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X228" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y228" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z228" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA228" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB228" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC228" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD228" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE228" s="7" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="229" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A229">
+    <row r="229" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A229" s="4">
         <v>228</v>
       </c>
-      <c r="B229" t="s">
+      <c r="B229" s="4" t="s">
         <v>537</v>
       </c>
-      <c r="C229" t="s">
+      <c r="C229" s="4" t="s">
         <v>564</v>
       </c>
-      <c r="D229" t="s">
+      <c r="D229" s="4" t="s">
         <v>565</v>
       </c>
-      <c r="E229" t="s">
+      <c r="E229" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F229">
+      <c r="F229" s="4">
         <v>2015</v>
       </c>
-      <c r="G229" s="2" t="s">
+      <c r="G229" s="10" t="s">
         <v>540</v>
       </c>
-      <c r="H229" s="3" t="s">
+      <c r="H229" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="I229" t="s">
+      <c r="I229" s="4" t="s">
         <v>537</v>
       </c>
-      <c r="J229" t="s">
+      <c r="J229" s="4" t="s">
         <v>541</v>
       </c>
-      <c r="K229" t="s">
+      <c r="K229" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="L229" t="s">
+      <c r="L229" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="M229" s="1">
+      <c r="M229" s="6">
         <v>42095</v>
       </c>
-      <c r="N229">
+      <c r="N229" s="4">
         <v>47.821566666666698</v>
       </c>
-      <c r="O229">
+      <c r="O229" s="4">
         <v>-122.578016666667</v>
       </c>
-      <c r="P229" t="s">
+      <c r="P229" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="Q229" t="s">
-        <v>40</v>
-      </c>
-      <c r="R229" t="s">
-        <v>43</v>
-      </c>
-      <c r="S229" t="s">
+      <c r="Q229" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="R229" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="S229" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="T229">
+      <c r="T229" s="4">
         <v>60</v>
       </c>
-      <c r="U229">
+      <c r="U229" s="4">
         <v>36</v>
       </c>
-      <c r="V229">
+      <c r="V229" s="4">
         <v>2160</v>
       </c>
-      <c r="W229">
+      <c r="W229" s="4">
         <v>320</v>
       </c>
-      <c r="X229">
+      <c r="X229" s="4">
         <v>8</v>
       </c>
-      <c r="Y229">
+      <c r="Y229" s="4">
         <v>1600</v>
       </c>
-      <c r="Z229">
+      <c r="Z229" s="4">
         <v>6400</v>
       </c>
-      <c r="AA229">
+      <c r="AA229" s="4">
         <v>2.9629629629629601</v>
       </c>
-      <c r="AB229">
+      <c r="AB229" s="4">
         <v>20</v>
       </c>
-      <c r="AC229" t="s">
+      <c r="AC229" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="AD229" t="s">
-        <v>43</v>
-      </c>
-      <c r="AE229" t="s">
+      <c r="AD229" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE229" s="4" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="230" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A230">
+    <row r="230" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A230" s="4">
         <v>229</v>
       </c>
-      <c r="B230" t="s">
+      <c r="B230" s="4" t="s">
         <v>537</v>
       </c>
-      <c r="C230" t="s">
+      <c r="C230" s="4" t="s">
         <v>566</v>
       </c>
-      <c r="D230" t="s">
+      <c r="D230" s="4" t="s">
         <v>565</v>
       </c>
-      <c r="E230" t="s">
+      <c r="E230" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F230">
+      <c r="F230" s="4">
         <v>2015</v>
       </c>
-      <c r="G230" s="2" t="s">
+      <c r="G230" s="10" t="s">
         <v>540</v>
       </c>
-      <c r="H230" s="3" t="s">
+      <c r="H230" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="I230" t="s">
+      <c r="I230" s="4" t="s">
         <v>537</v>
       </c>
-      <c r="J230" t="s">
+      <c r="J230" s="4" t="s">
         <v>541</v>
       </c>
-      <c r="K230" t="s">
+      <c r="K230" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="L230" t="s">
+      <c r="L230" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M230" s="1">
+      <c r="M230" s="6">
         <v>42095</v>
       </c>
-      <c r="N230">
+      <c r="N230" s="4">
         <v>47.821516666666703</v>
       </c>
-      <c r="O230">
+      <c r="O230" s="4">
         <v>-122.577216666667</v>
       </c>
-      <c r="P230" t="s">
+      <c r="P230" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="Q230" t="s">
-        <v>40</v>
-      </c>
-      <c r="R230" t="s">
-        <v>43</v>
-      </c>
-      <c r="S230" t="s">
+      <c r="Q230" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="R230" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="S230" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="T230" t="s">
-        <v>43</v>
-      </c>
-      <c r="U230" t="s">
-        <v>43</v>
-      </c>
-      <c r="V230" t="s">
-        <v>43</v>
-      </c>
-      <c r="W230" t="s">
-        <v>43</v>
-      </c>
-      <c r="X230" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y230" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z230" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA230" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB230" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC230" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD230" t="s">
-        <v>43</v>
-      </c>
-      <c r="AE230" t="s">
+      <c r="T230" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="U230" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="V230" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="W230" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X230" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y230" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z230" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA230" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB230" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC230" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD230" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE230" s="4" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="231" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A231">
+    <row r="231" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A231" s="4">
         <v>230</v>
       </c>
-      <c r="B231" t="s">
+      <c r="B231" s="4" t="s">
         <v>537</v>
       </c>
-      <c r="C231" t="s">
+      <c r="C231" s="4" t="s">
         <v>567</v>
       </c>
-      <c r="D231" t="s">
+      <c r="D231" s="4" t="s">
         <v>565</v>
       </c>
-      <c r="E231" t="s">
+      <c r="E231" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F231">
+      <c r="F231" s="4">
         <v>2015</v>
       </c>
-      <c r="G231" s="2" t="s">
+      <c r="G231" s="10" t="s">
         <v>540</v>
       </c>
-      <c r="H231" s="3" t="s">
+      <c r="H231" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="I231" t="s">
+      <c r="I231" s="4" t="s">
         <v>537</v>
       </c>
-      <c r="J231" t="s">
+      <c r="J231" s="4" t="s">
         <v>541</v>
       </c>
-      <c r="K231" t="s">
+      <c r="K231" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="L231" t="s">
+      <c r="L231" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M231" s="1">
+      <c r="M231" s="6">
         <v>42095</v>
       </c>
-      <c r="N231">
+      <c r="N231" s="4">
         <v>47.821183333333302</v>
       </c>
-      <c r="O231">
+      <c r="O231" s="4">
         <v>-122.577116666667</v>
       </c>
-      <c r="P231" t="s">
+      <c r="P231" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="Q231" t="s">
-        <v>40</v>
-      </c>
-      <c r="R231" t="s">
-        <v>43</v>
-      </c>
-      <c r="S231" t="s">
+      <c r="Q231" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="R231" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="S231" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="T231" t="s">
-        <v>43</v>
-      </c>
-      <c r="U231" t="s">
-        <v>43</v>
-      </c>
-      <c r="V231" t="s">
-        <v>43</v>
-      </c>
-      <c r="W231" t="s">
-        <v>43</v>
-      </c>
-      <c r="X231" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y231" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z231" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA231" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB231" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC231" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD231" t="s">
-        <v>43</v>
-      </c>
-      <c r="AE231" t="s">
+      <c r="T231" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="U231" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="V231" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="W231" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X231" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y231" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z231" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA231" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB231" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC231" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD231" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE231" s="4" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="232" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A232">
+    <row r="232" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A232" s="4">
         <v>231</v>
       </c>
-      <c r="B232" t="s">
+      <c r="B232" s="4" t="s">
         <v>537</v>
       </c>
-      <c r="C232" t="s">
+      <c r="C232" s="4" t="s">
         <v>568</v>
       </c>
-      <c r="D232" t="s">
+      <c r="D232" s="4" t="s">
         <v>565</v>
       </c>
-      <c r="E232" t="s">
+      <c r="E232" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F232">
+      <c r="F232" s="4">
         <v>2015</v>
       </c>
-      <c r="G232" s="2" t="s">
+      <c r="G232" s="10" t="s">
         <v>540</v>
       </c>
-      <c r="H232" s="3" t="s">
+      <c r="H232" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="I232" t="s">
+      <c r="I232" s="4" t="s">
         <v>537</v>
       </c>
-      <c r="J232" t="s">
+      <c r="J232" s="4" t="s">
         <v>541</v>
       </c>
-      <c r="K232" t="s">
+      <c r="K232" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="L232" t="s">
+      <c r="L232" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M232" s="1">
+      <c r="M232" s="6">
         <v>42095</v>
       </c>
-      <c r="N232">
+      <c r="N232" s="4">
         <v>47.8212166666667</v>
       </c>
-      <c r="O232">
+      <c r="O232" s="4">
         <v>-122.57791666666699</v>
       </c>
-      <c r="P232" t="s">
+      <c r="P232" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="Q232" t="s">
-        <v>40</v>
-      </c>
-      <c r="R232">
+      <c r="Q232" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="R232" s="4">
         <v>-1.8288</v>
       </c>
-      <c r="S232" t="s">
+      <c r="S232" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="T232" t="s">
-        <v>43</v>
-      </c>
-      <c r="U232" t="s">
-        <v>43</v>
-      </c>
-      <c r="V232" t="s">
-        <v>43</v>
-      </c>
-      <c r="W232" t="s">
-        <v>43</v>
-      </c>
-      <c r="X232" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y232" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z232" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA232" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB232" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC232" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD232" t="s">
-        <v>43</v>
-      </c>
-      <c r="AE232" t="s">
+      <c r="T232" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="U232" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="V232" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="W232" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X232" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y232" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z232" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA232" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB232" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC232" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD232" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE232" s="4" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="233" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A233">
+    <row r="233" spans="1:31" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A233" s="7">
         <v>232</v>
       </c>
-      <c r="B233" t="s">
+      <c r="B233" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="C233" t="s">
+      <c r="C233" s="7" t="s">
         <v>569</v>
       </c>
-      <c r="D233" t="s">
+      <c r="D233" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="E233" t="s">
+      <c r="E233" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="F233">
+      <c r="F233" s="7">
         <v>2015</v>
       </c>
-      <c r="G233" s="2" t="s">
+      <c r="G233" s="11" t="s">
         <v>540</v>
       </c>
-      <c r="H233" s="3" t="s">
+      <c r="H233" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="I233" t="s">
+      <c r="I233" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="J233" t="s">
+      <c r="J233" s="7" t="s">
         <v>541</v>
       </c>
-      <c r="K233" t="s">
+      <c r="K233" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="L233" t="s">
+      <c r="L233" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="M233" s="1">
+      <c r="M233" s="9">
         <v>42095</v>
       </c>
-      <c r="N233">
+      <c r="N233" s="7">
         <v>47.821666666666701</v>
       </c>
-      <c r="O233">
+      <c r="O233" s="7">
         <v>-122.57623333333299</v>
       </c>
-      <c r="P233" t="s">
+      <c r="P233" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="Q233" t="s">
-        <v>40</v>
-      </c>
-      <c r="R233" t="s">
-        <v>43</v>
-      </c>
-      <c r="S233" t="s">
+      <c r="Q233" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="R233" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="S233" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="T233">
+      <c r="T233" s="7">
         <v>60</v>
       </c>
-      <c r="U233">
+      <c r="U233" s="7">
         <v>36</v>
       </c>
-      <c r="V233">
+      <c r="V233" s="7">
         <v>2160</v>
       </c>
-      <c r="W233">
+      <c r="W233" s="7">
         <v>320</v>
       </c>
-      <c r="X233">
+      <c r="X233" s="7">
         <v>7.9649999999999999</v>
       </c>
-      <c r="Y233">
+      <c r="Y233" s="7">
         <v>1593</v>
       </c>
-      <c r="Z233">
+      <c r="Z233" s="7">
         <v>6372</v>
       </c>
-      <c r="AA233">
+      <c r="AA233" s="7">
         <v>2.95</v>
       </c>
-      <c r="AB233">
+      <c r="AB233" s="7">
         <v>19.912500000000001</v>
       </c>
-      <c r="AC233" t="s">
+      <c r="AC233" s="7" t="s">
         <v>542</v>
       </c>
-      <c r="AD233" t="s">
-        <v>43</v>
-      </c>
-      <c r="AE233" t="s">
+      <c r="AD233" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE233" s="7" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="234" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A234">
+    <row r="234" spans="1:31" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A234" s="7">
         <v>233</v>
       </c>
-      <c r="B234" t="s">
+      <c r="B234" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="C234" t="s">
+      <c r="C234" s="7" t="s">
         <v>571</v>
       </c>
-      <c r="D234" t="s">
+      <c r="D234" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="E234" t="s">
+      <c r="E234" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="F234">
+      <c r="F234" s="7">
         <v>2015</v>
       </c>
-      <c r="G234" s="2" t="s">
+      <c r="G234" s="11" t="s">
         <v>540</v>
       </c>
-      <c r="H234" s="3" t="s">
+      <c r="H234" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="I234" t="s">
+      <c r="I234" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="J234" t="s">
+      <c r="J234" s="7" t="s">
         <v>541</v>
       </c>
-      <c r="K234" t="s">
+      <c r="K234" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="L234" t="s">
+      <c r="L234" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="M234" s="1">
+      <c r="M234" s="9">
         <v>42095</v>
       </c>
-      <c r="N234">
+      <c r="N234" s="7">
         <v>47.821533333333299</v>
       </c>
-      <c r="O234">
+      <c r="O234" s="7">
         <v>-122.57538333333299</v>
       </c>
-      <c r="P234" t="s">
+      <c r="P234" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="Q234" t="s">
-        <v>40</v>
-      </c>
-      <c r="R234">
+      <c r="Q234" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="R234" s="7">
         <v>-2.7431999999999999</v>
       </c>
-      <c r="S234" t="s">
+      <c r="S234" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="T234" t="s">
-        <v>43</v>
-      </c>
-      <c r="U234" t="s">
-        <v>43</v>
-      </c>
-      <c r="V234" t="s">
-        <v>43</v>
-      </c>
-      <c r="W234" t="s">
-        <v>43</v>
-      </c>
-      <c r="X234" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y234" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z234" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA234" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB234" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC234" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD234" t="s">
-        <v>43</v>
-      </c>
-      <c r="AE234" t="s">
+      <c r="T234" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="U234" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="V234" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="W234" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X234" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y234" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z234" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA234" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB234" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC234" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD234" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE234" s="7" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="235" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A235">
+    <row r="235" spans="1:31" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A235" s="7">
         <v>234</v>
       </c>
-      <c r="B235" t="s">
+      <c r="B235" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="C235" t="s">
+      <c r="C235" s="7" t="s">
         <v>572</v>
       </c>
-      <c r="D235" t="s">
+      <c r="D235" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="E235" t="s">
+      <c r="E235" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="F235">
+      <c r="F235" s="7">
         <v>2015</v>
       </c>
-      <c r="G235" s="2" t="s">
+      <c r="G235" s="11" t="s">
         <v>540</v>
       </c>
-      <c r="H235" s="3" t="s">
+      <c r="H235" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="I235" t="s">
+      <c r="I235" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="J235" t="s">
+      <c r="J235" s="7" t="s">
         <v>541</v>
       </c>
-      <c r="K235" t="s">
+      <c r="K235" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="L235" t="s">
+      <c r="L235" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="M235" s="1">
+      <c r="M235" s="9">
         <v>42095</v>
       </c>
-      <c r="N235">
+      <c r="N235" s="7">
         <v>47.8212166666667</v>
       </c>
-      <c r="O235">
+      <c r="O235" s="7">
         <v>-122.575283333333</v>
       </c>
-      <c r="P235" t="s">
+      <c r="P235" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="Q235" t="s">
-        <v>40</v>
-      </c>
-      <c r="R235" t="s">
-        <v>43</v>
-      </c>
-      <c r="S235" t="s">
+      <c r="Q235" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="R235" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="S235" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="T235" t="s">
-        <v>43</v>
-      </c>
-      <c r="U235" t="s">
-        <v>43</v>
-      </c>
-      <c r="V235" t="s">
-        <v>43</v>
-      </c>
-      <c r="W235" t="s">
-        <v>43</v>
-      </c>
-      <c r="X235" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y235" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z235" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA235" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB235" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC235" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD235" t="s">
-        <v>43</v>
-      </c>
-      <c r="AE235" t="s">
+      <c r="T235" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="U235" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="V235" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="W235" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X235" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y235" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z235" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA235" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB235" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC235" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD235" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE235" s="7" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="236" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A236">
+    <row r="236" spans="1:31" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A236" s="7">
         <v>235</v>
       </c>
-      <c r="B236" t="s">
+      <c r="B236" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="C236" t="s">
+      <c r="C236" s="7" t="s">
         <v>573</v>
       </c>
-      <c r="D236" t="s">
+      <c r="D236" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="E236" t="s">
+      <c r="E236" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="F236">
+      <c r="F236" s="7">
         <v>2015</v>
       </c>
-      <c r="G236" s="2" t="s">
+      <c r="G236" s="11" t="s">
         <v>540</v>
       </c>
-      <c r="H236" s="3" t="s">
+      <c r="H236" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="I236" t="s">
+      <c r="I236" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="J236" t="s">
+      <c r="J236" s="7" t="s">
         <v>541</v>
       </c>
-      <c r="K236" t="s">
+      <c r="K236" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="L236" t="s">
+      <c r="L236" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="M236" s="1">
+      <c r="M236" s="9">
         <v>42095</v>
       </c>
-      <c r="N236">
+      <c r="N236" s="7">
         <v>47.821283333333298</v>
       </c>
-      <c r="O236">
+      <c r="O236" s="7">
         <v>-122.57618333333301</v>
       </c>
-      <c r="P236" t="s">
+      <c r="P236" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="Q236" t="s">
-        <v>40</v>
-      </c>
-      <c r="R236" t="s">
-        <v>43</v>
-      </c>
-      <c r="S236" t="s">
+      <c r="Q236" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="R236" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="S236" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="T236" t="s">
-        <v>43</v>
-      </c>
-      <c r="U236" t="s">
-        <v>43</v>
-      </c>
-      <c r="V236" t="s">
-        <v>43</v>
-      </c>
-      <c r="W236" t="s">
-        <v>43</v>
-      </c>
-      <c r="X236" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y236" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z236" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA236" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB236" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC236" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD236" t="s">
-        <v>43</v>
-      </c>
-      <c r="AE236" t="s">
+      <c r="T236" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="U236" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="V236" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="W236" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X236" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y236" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z236" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA236" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB236" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC236" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD236" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE236" s="7" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="237" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>236</v>
       </c>
@@ -25579,7 +25580,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="238" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>237</v>
       </c>
@@ -25674,7 +25675,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="239" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>238</v>
       </c>
@@ -25769,7 +25770,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="240" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>239</v>
       </c>
@@ -25864,7 +25865,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="241" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>240</v>
       </c>
@@ -25959,7 +25960,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="242" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>241</v>
       </c>
@@ -26054,7 +26055,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="243" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>242</v>
       </c>
@@ -26149,7 +26150,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="244" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>243</v>
       </c>
@@ -26244,7 +26245,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="245" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>244</v>
       </c>
@@ -26339,7 +26340,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="246" spans="1:31" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="4">
         <v>245</v>
       </c>
@@ -26434,7 +26435,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="247" spans="1:31" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="4">
         <v>246</v>
       </c>
@@ -26529,7 +26530,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="248" spans="1:31" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="4">
         <v>247</v>
       </c>
@@ -26624,7 +26625,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="249" spans="1:31" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="4">
         <v>248</v>
       </c>
@@ -26719,7 +26720,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="250" spans="1:31" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="4">
         <v>249</v>
       </c>
@@ -26814,7 +26815,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="251" spans="1:31" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="4">
         <v>250</v>
       </c>
@@ -26909,7 +26910,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="252" spans="1:31" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="4">
         <v>251</v>
       </c>
@@ -27004,7 +27005,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="253" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>252</v>
       </c>
@@ -27099,7 +27100,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="254" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>253</v>
       </c>
@@ -27194,7 +27195,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="255" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>254</v>
       </c>
@@ -27289,7 +27290,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="256" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>255</v>
       </c>
@@ -27384,7 +27385,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="257" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>256</v>
       </c>
@@ -27479,7 +27480,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="258" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>257</v>
       </c>
@@ -27574,7 +27575,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="259" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>258</v>
       </c>
@@ -27669,7 +27670,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="260" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>259</v>
       </c>
@@ -27764,7 +27765,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="261" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>260</v>
       </c>
@@ -27859,7 +27860,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="262" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>261</v>
       </c>
@@ -27954,7 +27955,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="263" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>262</v>
       </c>
@@ -28049,7 +28050,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="264" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>263</v>
       </c>
@@ -28144,7 +28145,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="265" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>264</v>
       </c>
@@ -28239,7 +28240,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="266" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>265</v>
       </c>
@@ -28334,7 +28335,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="267" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>266</v>
       </c>
@@ -28429,7 +28430,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="268" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>267</v>
       </c>
@@ -28524,7 +28525,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="269" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>268</v>
       </c>
@@ -28619,7 +28620,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="270" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>269</v>
       </c>
@@ -28714,7 +28715,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="271" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>270</v>
       </c>
@@ -28809,7 +28810,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="272" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>271</v>
       </c>
@@ -28904,7 +28905,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="273" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>272</v>
       </c>
@@ -28999,7 +29000,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="274" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>273</v>
       </c>
@@ -29094,7 +29095,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="275" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>274</v>
       </c>
@@ -29189,7 +29190,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="276" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>275</v>
       </c>
@@ -29284,7 +29285,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="277" spans="1:31" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="4">
         <v>276</v>
       </c>
@@ -29379,7 +29380,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="278" spans="1:31" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="4">
         <v>277</v>
       </c>
@@ -29474,7 +29475,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="279" spans="1:31" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="4">
         <v>278</v>
       </c>
@@ -29569,7 +29570,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="280" spans="1:31" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="4">
         <v>279</v>
       </c>
@@ -29664,7 +29665,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="281" spans="1:31" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="4">
         <v>280</v>
       </c>
@@ -29759,7 +29760,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="282" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>281</v>
       </c>
@@ -29854,387 +29855,387 @@
         <v>44</v>
       </c>
     </row>
-    <row r="283" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A283">
+    <row r="283" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A283" s="4">
         <v>282</v>
       </c>
-      <c r="B283" t="s">
+      <c r="B283" s="4" t="s">
         <v>686</v>
       </c>
-      <c r="C283" t="s">
+      <c r="C283" s="4" t="s">
         <v>691</v>
       </c>
-      <c r="D283" t="s">
+      <c r="D283" s="4" t="s">
         <v>692</v>
       </c>
-      <c r="E283" t="s">
+      <c r="E283" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F283">
+      <c r="F283" s="4">
         <v>2015</v>
       </c>
-      <c r="G283" t="s">
+      <c r="G283" s="4" t="s">
         <v>689</v>
       </c>
-      <c r="H283" s="3" t="s">
+      <c r="H283" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="I283" t="s">
+      <c r="I283" s="4" t="s">
         <v>690</v>
       </c>
-      <c r="J283" t="s">
+      <c r="J283" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="K283" t="s">
+      <c r="K283" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="L283" t="s">
+      <c r="L283" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="M283" s="1">
+      <c r="M283" s="6">
         <v>42128</v>
       </c>
-      <c r="N283">
+      <c r="N283" s="4">
         <v>47.145733333333297</v>
       </c>
-      <c r="O283">
+      <c r="O283" s="4">
         <v>-122.893183333333</v>
       </c>
-      <c r="P283" t="s">
+      <c r="P283" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="Q283" t="s">
-        <v>40</v>
-      </c>
-      <c r="R283">
+      <c r="Q283" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="R283" s="4">
         <v>-2.286</v>
       </c>
-      <c r="S283" t="s">
+      <c r="S283" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="T283">
+      <c r="T283" s="4">
         <v>55</v>
       </c>
-      <c r="U283">
+      <c r="U283" s="4">
         <v>30</v>
       </c>
-      <c r="V283">
+      <c r="V283" s="4">
         <v>1650</v>
       </c>
-      <c r="W283">
+      <c r="W283" s="4">
         <v>220</v>
       </c>
-      <c r="X283">
+      <c r="X283" s="4">
         <v>11.225</v>
       </c>
-      <c r="Y283">
+      <c r="Y283" s="4">
         <v>2245</v>
       </c>
-      <c r="Z283">
+      <c r="Z283" s="4">
         <v>8980</v>
       </c>
-      <c r="AA283">
+      <c r="AA283" s="4">
         <v>5.4424242424242397</v>
       </c>
-      <c r="AB283">
+      <c r="AB283" s="4">
         <v>40.818181818181799</v>
       </c>
-      <c r="AC283" t="s">
+      <c r="AC283" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="AD283" t="s">
+      <c r="AD283" s="4" t="s">
         <v>693</v>
       </c>
-      <c r="AE283" t="s">
+      <c r="AE283" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="284" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A284">
+    <row r="284" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A284" s="4">
         <v>283</v>
       </c>
-      <c r="B284" t="s">
+      <c r="B284" s="4" t="s">
         <v>686</v>
       </c>
-      <c r="C284" t="s">
+      <c r="C284" s="4" t="s">
         <v>694</v>
       </c>
-      <c r="D284" t="s">
+      <c r="D284" s="4" t="s">
         <v>692</v>
       </c>
-      <c r="E284" t="s">
+      <c r="E284" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F284">
+      <c r="F284" s="4">
         <v>2015</v>
       </c>
-      <c r="G284" t="s">
+      <c r="G284" s="4" t="s">
         <v>689</v>
       </c>
-      <c r="H284" s="3" t="s">
+      <c r="H284" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="I284" t="s">
+      <c r="I284" s="4" t="s">
         <v>690</v>
       </c>
-      <c r="J284" t="s">
+      <c r="J284" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="K284" t="s">
+      <c r="K284" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="L284" t="s">
+      <c r="L284" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M284" s="1">
+      <c r="M284" s="6">
         <v>42128</v>
       </c>
-      <c r="N284">
+      <c r="N284" s="4">
         <v>47.145633333333301</v>
       </c>
-      <c r="O284">
+      <c r="O284" s="4">
         <v>-122.892466666667</v>
       </c>
-      <c r="P284" t="s">
+      <c r="P284" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="Q284" t="s">
-        <v>40</v>
-      </c>
-      <c r="R284" t="s">
-        <v>43</v>
-      </c>
-      <c r="S284" t="s">
+      <c r="Q284" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="R284" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="S284" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="T284" t="s">
-        <v>43</v>
-      </c>
-      <c r="U284" t="s">
-        <v>43</v>
-      </c>
-      <c r="V284" t="s">
-        <v>43</v>
-      </c>
-      <c r="W284" t="s">
-        <v>43</v>
-      </c>
-      <c r="X284" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y284" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z284" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA284" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB284" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC284" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD284" t="s">
-        <v>43</v>
-      </c>
-      <c r="AE284" t="s">
+      <c r="T284" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="U284" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="V284" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="W284" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X284" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y284" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z284" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA284" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB284" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC284" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD284" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE284" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="285" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A285">
+    <row r="285" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A285" s="4">
         <v>284</v>
       </c>
-      <c r="B285" t="s">
+      <c r="B285" s="4" t="s">
         <v>686</v>
       </c>
-      <c r="C285" t="s">
+      <c r="C285" s="4" t="s">
         <v>695</v>
       </c>
-      <c r="D285" t="s">
+      <c r="D285" s="4" t="s">
         <v>692</v>
       </c>
-      <c r="E285" t="s">
+      <c r="E285" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F285">
+      <c r="F285" s="4">
         <v>2015</v>
       </c>
-      <c r="G285" t="s">
+      <c r="G285" s="4" t="s">
         <v>689</v>
       </c>
-      <c r="H285" s="3" t="s">
+      <c r="H285" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="I285" t="s">
+      <c r="I285" s="4" t="s">
         <v>690</v>
       </c>
-      <c r="J285" t="s">
+      <c r="J285" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="K285" t="s">
+      <c r="K285" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="L285" t="s">
+      <c r="L285" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M285" s="1">
+      <c r="M285" s="6">
         <v>42128</v>
       </c>
-      <c r="N285">
+      <c r="N285" s="4">
         <v>47.145400000000002</v>
       </c>
-      <c r="O285">
+      <c r="O285" s="4">
         <v>-122.89255</v>
       </c>
-      <c r="P285" t="s">
+      <c r="P285" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="Q285" t="s">
-        <v>40</v>
-      </c>
-      <c r="R285" t="s">
-        <v>43</v>
-      </c>
-      <c r="S285" t="s">
+      <c r="Q285" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="R285" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="S285" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="T285" t="s">
-        <v>43</v>
-      </c>
-      <c r="U285" t="s">
-        <v>43</v>
-      </c>
-      <c r="V285" t="s">
-        <v>43</v>
-      </c>
-      <c r="W285" t="s">
-        <v>43</v>
-      </c>
-      <c r="X285" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y285" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z285" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA285" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB285" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC285" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD285" t="s">
-        <v>43</v>
-      </c>
-      <c r="AE285" t="s">
+      <c r="T285" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="U285" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="V285" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="W285" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X285" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y285" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z285" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA285" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB285" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC285" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD285" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE285" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="286" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A286">
+    <row r="286" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A286" s="4">
         <v>285</v>
       </c>
-      <c r="B286" t="s">
+      <c r="B286" s="4" t="s">
         <v>686</v>
       </c>
-      <c r="C286" t="s">
+      <c r="C286" s="4" t="s">
         <v>696</v>
       </c>
-      <c r="D286" t="s">
+      <c r="D286" s="4" t="s">
         <v>692</v>
       </c>
-      <c r="E286" t="s">
+      <c r="E286" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F286">
+      <c r="F286" s="4">
         <v>2015</v>
       </c>
-      <c r="G286" t="s">
+      <c r="G286" s="4" t="s">
         <v>689</v>
       </c>
-      <c r="H286" s="3" t="s">
+      <c r="H286" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="I286" t="s">
+      <c r="I286" s="4" t="s">
         <v>690</v>
       </c>
-      <c r="J286" t="s">
+      <c r="J286" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="K286" t="s">
+      <c r="K286" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="L286" t="s">
+      <c r="L286" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M286" s="1">
+      <c r="M286" s="6">
         <v>42128</v>
       </c>
-      <c r="N286">
+      <c r="N286" s="4">
         <v>47.14555</v>
       </c>
-      <c r="O286">
+      <c r="O286" s="4">
         <v>-122.893233333333</v>
       </c>
-      <c r="P286" t="s">
+      <c r="P286" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="Q286" t="s">
-        <v>40</v>
-      </c>
-      <c r="R286">
+      <c r="Q286" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="R286" s="4">
         <v>-1.1277600000000001</v>
       </c>
-      <c r="S286" t="s">
+      <c r="S286" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="T286" t="s">
-        <v>43</v>
-      </c>
-      <c r="U286" t="s">
-        <v>43</v>
-      </c>
-      <c r="V286" t="s">
-        <v>43</v>
-      </c>
-      <c r="W286" t="s">
-        <v>43</v>
-      </c>
-      <c r="X286" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y286" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z286" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA286" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB286" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC286" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD286" t="s">
-        <v>43</v>
-      </c>
-      <c r="AE286" t="s">
+      <c r="T286" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="U286" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="V286" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="W286" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X286" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y286" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z286" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA286" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB286" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC286" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD286" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE286" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="287" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>286</v>
       </c>
@@ -30329,7 +30330,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="288" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>287</v>
       </c>
@@ -30424,7 +30425,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="289" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>288</v>
       </c>

--- a/p_gps_pts.xlsx
+++ b/p_gps_pts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stateofwa-my.sharepoint.com/personal/peter_dowty_dnr_wa_gov/Documents/projects/seagrass_restoration_data_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{482DCFCD-CB29-4C6F-A4E2-D15E2062173E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C04B233-E9A2-4D28-9E31-7FF6BE17617E}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{482DCFCD-CB29-4C6F-A4E2-D15E2062173E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08A187CE-FE0C-4EAD-A94B-5CA8F6636FC5}"/>
   <bookViews>
     <workbookView xWindow="90" yWindow="45" windowWidth="28320" windowHeight="15330" xr2:uid="{472C6C18-3318-42E5-B3DE-BCE9F97FEFF7}"/>
   </bookViews>
@@ -3044,8 +3044,8 @@
     <col min="6" max="6" width="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="17.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.140625" bestFit="1" customWidth="1"/>

--- a/p_gps_pts.xlsx
+++ b/p_gps_pts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stateofwa-my.sharepoint.com/personal/peter_dowty_dnr_wa_gov/Documents/projects/seagrass_restoration_data_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{482DCFCD-CB29-4C6F-A4E2-D15E2062173E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08A187CE-FE0C-4EAD-A94B-5CA8F6636FC5}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{482DCFCD-CB29-4C6F-A4E2-D15E2062173E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8C550D9-258D-407C-BB9C-DC781A5739B4}"/>
   <bookViews>
     <workbookView xWindow="90" yWindow="45" windowWidth="28320" windowHeight="15330" xr2:uid="{472C6C18-3318-42E5-B3DE-BCE9F97FEFF7}"/>
   </bookViews>
@@ -3052,8 +3052,8 @@
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="17.7109375" hidden="1" customWidth="1"/>
     <col min="19" max="19" width="16" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="22.7109375" bestFit="1" customWidth="1"/>
